--- a/artfynd/A 48961-2024 artfynd.xlsx
+++ b/artfynd/A 48961-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125070603</v>
+        <v>125073564</v>
       </c>
       <c r="B2" t="n">
-        <v>96979</v>
+        <v>79891</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Mpd</t>
+          <t>Svarttjärnsåsen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597467</v>
+        <v>597336</v>
       </c>
       <c r="R2" t="n">
-        <v>6925971</v>
+        <v>6926029</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125066963</v>
+        <v>125067978</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597575</v>
+        <v>597505</v>
       </c>
       <c r="R3" t="n">
-        <v>6925842</v>
+        <v>6925873</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125066674</v>
+        <v>125066963</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,39 +925,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597627</v>
+        <v>597575</v>
       </c>
       <c r="R4" t="n">
-        <v>6925859</v>
+        <v>6925842</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:39</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,7 +1021,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125067552</v>
+        <v>125067330</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597549</v>
+        <v>597572</v>
       </c>
       <c r="R5" t="n">
-        <v>6925866</v>
+        <v>6925875</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125067179</v>
+        <v>125069753</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,39 +1149,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597556</v>
+        <v>597481</v>
       </c>
       <c r="R6" t="n">
-        <v>6925836</v>
+        <v>6926022</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,12 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:07</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125067738</v>
+        <v>125067552</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,39 +1261,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597512</v>
+        <v>597549</v>
       </c>
       <c r="R7" t="n">
-        <v>6925861</v>
+        <v>6925866</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,12 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:28</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125069753</v>
+        <v>125069803</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,24 +1373,29 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
@@ -1452,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1462,7 +1447,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1489,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125067926</v>
+        <v>125069232</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1505,39 +1490,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597505</v>
+        <v>597507</v>
       </c>
       <c r="R9" t="n">
-        <v>6925873</v>
+        <v>6925959</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1569,7 +1549,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1579,12 +1559,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:37</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1611,10 +1586,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125067046</v>
+        <v>125070762</v>
       </c>
       <c r="B10" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1623,31 +1598,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1656,10 +1631,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597572</v>
+        <v>597398</v>
       </c>
       <c r="R10" t="n">
-        <v>6925829</v>
+        <v>6925953</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1691,7 +1666,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1701,7 +1676,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1728,10 +1708,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125067330</v>
+        <v>125066854</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1740,38 +1720,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597572</v>
+        <v>597598</v>
       </c>
       <c r="R11" t="n">
-        <v>6925875</v>
+        <v>6925850</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1803,7 +1787,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1813,7 +1797,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1840,10 +1824,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125070329</v>
+        <v>125066674</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1856,34 +1840,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597477</v>
+        <v>597627</v>
       </c>
       <c r="R12" t="n">
-        <v>6925984</v>
+        <v>6925859</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1915,7 +1904,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1925,7 +1914,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>08:39</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1952,10 +1946,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125067365</v>
+        <v>125073504</v>
       </c>
       <c r="B13" t="n">
-        <v>96979</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1964,38 +1958,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Mpd</t>
+          <t>Svarttjärnsåsen, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>597572</v>
+        <v>597276</v>
       </c>
       <c r="R13" t="n">
-        <v>6925875</v>
+        <v>6926060</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2027,7 +2026,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2037,7 +2036,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2064,10 +2068,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125071368</v>
+        <v>125071010</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2080,34 +2084,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Svarttjärnsåsen, Mpd</t>
+          <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>597351</v>
+        <v>597422</v>
       </c>
       <c r="R14" t="n">
-        <v>6926064</v>
+        <v>6925982</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2139,7 +2148,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2149,7 +2158,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2176,7 +2190,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125073504</v>
+        <v>125068260</v>
       </c>
       <c r="B15" t="n">
         <v>57513</v>
@@ -2212,19 +2226,19 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Svarttjärnsåsen, Mpd</t>
+          <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>597276</v>
+        <v>597492</v>
       </c>
       <c r="R15" t="n">
-        <v>6926060</v>
+        <v>6925938</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2256,7 +2270,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2266,7 +2280,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2298,10 +2312,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125073564</v>
+        <v>125066707</v>
       </c>
       <c r="B16" t="n">
-        <v>79891</v>
+        <v>57995</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2314,34 +2328,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>103018</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Svarttjärnsåsen, Mpd</t>
+          <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>597336</v>
+        <v>597609</v>
       </c>
       <c r="R16" t="n">
-        <v>6926029</v>
+        <v>6925861</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2373,7 +2392,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2383,7 +2402,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2410,10 +2429,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125066854</v>
+        <v>125071368</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2422,42 +2441,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Mpd</t>
+          <t>Svarttjärnsåsen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>597598</v>
+        <v>597351</v>
       </c>
       <c r="R17" t="n">
-        <v>6925850</v>
+        <v>6926064</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2489,7 +2504,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2499,7 +2514,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2526,10 +2541,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125068606</v>
+        <v>125070329</v>
       </c>
       <c r="B18" t="n">
-        <v>56722</v>
+        <v>91012</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2538,43 +2553,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>597492</v>
+        <v>597477</v>
       </c>
       <c r="R18" t="n">
-        <v>6925938</v>
+        <v>6925984</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2606,7 +2616,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2616,7 +2626,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2643,10 +2653,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125070762</v>
+        <v>125067046</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2655,31 +2665,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2688,10 +2698,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>597398</v>
+        <v>597572</v>
       </c>
       <c r="R19" t="n">
-        <v>6925953</v>
+        <v>6925829</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2723,7 +2733,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2733,12 +2743,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:04</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2765,10 +2770,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125067837</v>
+        <v>125067179</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2781,34 +2786,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>597505</v>
+        <v>597556</v>
       </c>
       <c r="R20" t="n">
-        <v>6925873</v>
+        <v>6925836</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2840,7 +2850,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2850,7 +2860,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2877,10 +2892,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125071236</v>
+        <v>125067365</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>96979</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2889,43 +2904,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>597394</v>
+        <v>597572</v>
       </c>
       <c r="R21" t="n">
-        <v>6926034</v>
+        <v>6925875</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2957,7 +2967,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2967,12 +2977,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2999,10 +3004,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125066707</v>
+        <v>125071236</v>
       </c>
       <c r="B22" t="n">
-        <v>57995</v>
+        <v>57513</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3015,27 +3020,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103018</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3044,10 +3049,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>597609</v>
+        <v>597394</v>
       </c>
       <c r="R22" t="n">
-        <v>6925861</v>
+        <v>6926034</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3079,7 +3084,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3089,7 +3094,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3116,10 +3126,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125071010</v>
+        <v>125071663</v>
       </c>
       <c r="B23" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3132,16 +3142,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3157,14 +3167,14 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Mpd</t>
+          <t>Svarttjärnsåsen, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>597422</v>
+        <v>597242</v>
       </c>
       <c r="R23" t="n">
-        <v>6925982</v>
+        <v>6926157</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3196,7 +3206,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3206,12 +3216,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3238,7 +3243,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125069232</v>
+        <v>125067837</v>
       </c>
       <c r="B24" t="n">
         <v>78810</v>
@@ -3278,10 +3283,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>597507</v>
+        <v>597505</v>
       </c>
       <c r="R24" t="n">
-        <v>6925959</v>
+        <v>6925873</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3313,7 +3318,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3323,7 +3328,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3350,10 +3355,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125071663</v>
+        <v>125067738</v>
       </c>
       <c r="B25" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3366,16 +3371,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3391,14 +3396,14 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Svarttjärnsåsen, Mpd</t>
+          <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>597242</v>
+        <v>597512</v>
       </c>
       <c r="R25" t="n">
-        <v>6926157</v>
+        <v>6925861</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3430,7 +3435,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3440,7 +3445,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3467,10 +3477,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125068260</v>
+        <v>125068606</v>
       </c>
       <c r="B26" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3479,31 +3489,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3547,7 +3557,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3557,12 +3567,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:55</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3589,10 +3594,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125069803</v>
+        <v>125070603</v>
       </c>
       <c r="B27" t="n">
-        <v>56714</v>
+        <v>96979</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3601,43 +3606,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102612</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>597481</v>
+        <v>597467</v>
       </c>
       <c r="R27" t="n">
-        <v>6926022</v>
+        <v>6925971</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 48961-2024 artfynd.xlsx
+++ b/artfynd/A 48961-2024 artfynd.xlsx
@@ -1133,7 +1133,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125069753</v>
+        <v>125067552</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597481</v>
+        <v>597549</v>
       </c>
       <c r="R6" t="n">
-        <v>6926022</v>
+        <v>6925866</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,7 +1245,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125067552</v>
+        <v>125069753</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597549</v>
+        <v>597481</v>
       </c>
       <c r="R7" t="n">
-        <v>6925866</v>
+        <v>6926022</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1824,7 +1824,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125066674</v>
+        <v>125073504</v>
       </c>
       <c r="B12" t="n">
         <v>57513</v>
@@ -1860,19 +1860,19 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Mpd</t>
+          <t>Svarttjärnsåsen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597627</v>
+        <v>597276</v>
       </c>
       <c r="R12" t="n">
-        <v>6925859</v>
+        <v>6926060</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1946,7 +1946,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125073504</v>
+        <v>125066674</v>
       </c>
       <c r="B13" t="n">
         <v>57513</v>
@@ -1982,19 +1982,19 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Svarttjärnsåsen, Mpd</t>
+          <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>597276</v>
+        <v>597627</v>
       </c>
       <c r="R13" t="n">
-        <v>6926060</v>
+        <v>6925859</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2036,12 +2036,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2068,7 +2068,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125071010</v>
+        <v>125068260</v>
       </c>
       <c r="B14" t="n">
         <v>57513</v>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>597422</v>
+        <v>597492</v>
       </c>
       <c r="R14" t="n">
-        <v>6925982</v>
+        <v>6925938</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2190,7 +2190,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125068260</v>
+        <v>125071010</v>
       </c>
       <c r="B15" t="n">
         <v>57513</v>
@@ -2235,10 +2235,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>597492</v>
+        <v>597422</v>
       </c>
       <c r="R15" t="n">
-        <v>6925938</v>
+        <v>6925982</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2312,10 +2312,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125066707</v>
+        <v>125071368</v>
       </c>
       <c r="B16" t="n">
-        <v>57995</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2328,39 +2328,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103018</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Mpd</t>
+          <t>Svarttjärnsåsen, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>597609</v>
+        <v>597351</v>
       </c>
       <c r="R16" t="n">
-        <v>6925861</v>
+        <v>6926064</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2392,7 +2387,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2402,7 +2397,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2429,10 +2424,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125071368</v>
+        <v>125070329</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2445,34 +2440,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Svarttjärnsåsen, Mpd</t>
+          <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>597351</v>
+        <v>597477</v>
       </c>
       <c r="R17" t="n">
-        <v>6926064</v>
+        <v>6925984</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2504,7 +2499,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2514,7 +2509,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2541,10 +2536,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125070329</v>
+        <v>125066707</v>
       </c>
       <c r="B18" t="n">
-        <v>91012</v>
+        <v>57995</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2557,34 +2552,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>103018</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>597477</v>
+        <v>597609</v>
       </c>
       <c r="R18" t="n">
-        <v>6925984</v>
+        <v>6925861</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3126,10 +3126,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125071663</v>
+        <v>125067837</v>
       </c>
       <c r="B23" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3142,39 +3142,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Svarttjärnsåsen, Mpd</t>
+          <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>597242</v>
+        <v>597505</v>
       </c>
       <c r="R23" t="n">
-        <v>6926157</v>
+        <v>6925873</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3206,7 +3201,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3216,7 +3211,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3243,10 +3238,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125067837</v>
+        <v>125071663</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3259,34 +3254,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Mpd</t>
+          <t>Svarttjärnsåsen, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>597505</v>
+        <v>597242</v>
       </c>
       <c r="R24" t="n">
-        <v>6925873</v>
+        <v>6926157</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3318,7 +3318,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 48961-2024 artfynd.xlsx
+++ b/artfynd/A 48961-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125073564</v>
+        <v>125071236</v>
       </c>
       <c r="B2" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Svarttjärnsåsen, Mpd</t>
+          <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597336</v>
+        <v>597394</v>
       </c>
       <c r="R2" t="n">
-        <v>6926029</v>
+        <v>6926034</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125067978</v>
+        <v>125067365</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>96979</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,43 +809,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597505</v>
+        <v>597572</v>
       </c>
       <c r="R3" t="n">
-        <v>6925873</v>
+        <v>6925875</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:39</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125066963</v>
+        <v>125070603</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>96979</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,25 +921,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597575</v>
+        <v>597467</v>
       </c>
       <c r="R4" t="n">
-        <v>6925842</v>
+        <v>6925971</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125067330</v>
+        <v>125068606</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,38 +1033,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597572</v>
+        <v>597492</v>
       </c>
       <c r="R5" t="n">
-        <v>6925875</v>
+        <v>6925938</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,7 +1138,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125067552</v>
+        <v>125069753</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1173,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597549</v>
+        <v>597481</v>
       </c>
       <c r="R6" t="n">
-        <v>6925866</v>
+        <v>6926022</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,7 +1250,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125069753</v>
+        <v>125071368</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1281,14 +1286,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Mpd</t>
+          <t>Svarttjärnsåsen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597481</v>
+        <v>597351</v>
       </c>
       <c r="R7" t="n">
-        <v>6926022</v>
+        <v>6926064</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1474,7 +1479,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125069232</v>
+        <v>125067330</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1514,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597507</v>
+        <v>597572</v>
       </c>
       <c r="R9" t="n">
-        <v>6925959</v>
+        <v>6925875</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1549,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1559,7 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,10 +1591,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125070762</v>
+        <v>125066707</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>57995</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,27 +1607,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>103018</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1631,10 +1636,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597398</v>
+        <v>597609</v>
       </c>
       <c r="R10" t="n">
-        <v>6925953</v>
+        <v>6925861</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1666,7 +1671,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1676,12 +1681,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:04</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1708,10 +1708,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125066854</v>
+        <v>125071010</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1720,30 +1720,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1752,10 +1753,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597598</v>
+        <v>597422</v>
       </c>
       <c r="R11" t="n">
-        <v>6925850</v>
+        <v>6925982</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1787,7 +1788,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1797,7 +1798,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1824,10 +1830,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125073504</v>
+        <v>125071663</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1840,16 +1846,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1860,7 +1866,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1869,10 +1875,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597276</v>
+        <v>597242</v>
       </c>
       <c r="R12" t="n">
-        <v>6926060</v>
+        <v>6926157</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1904,7 +1910,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1914,12 +1920,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1946,10 +1947,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125066674</v>
+        <v>125066854</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1958,31 +1959,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>597627</v>
+        <v>597598</v>
       </c>
       <c r="R13" t="n">
-        <v>6925859</v>
+        <v>6925850</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2036,12 +2036,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:39</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2068,7 +2063,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125068260</v>
+        <v>125070762</v>
       </c>
       <c r="B14" t="n">
         <v>57513</v>
@@ -2104,7 +2099,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2113,10 +2108,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>597492</v>
+        <v>597398</v>
       </c>
       <c r="R14" t="n">
-        <v>6925938</v>
+        <v>6925953</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2148,7 +2143,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2158,7 +2153,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2190,7 +2185,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125071010</v>
+        <v>125067738</v>
       </c>
       <c r="B15" t="n">
         <v>57513</v>
@@ -2235,10 +2230,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>597422</v>
+        <v>597512</v>
       </c>
       <c r="R15" t="n">
-        <v>6925982</v>
+        <v>6925861</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2270,7 +2265,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2280,7 +2275,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2312,10 +2307,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125071368</v>
+        <v>125068260</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2328,34 +2323,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Svarttjärnsåsen, Mpd</t>
+          <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>597351</v>
+        <v>597492</v>
       </c>
       <c r="R16" t="n">
-        <v>6926064</v>
+        <v>6925938</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2387,7 +2387,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2397,7 +2397,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2424,10 +2429,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125070329</v>
+        <v>125067978</v>
       </c>
       <c r="B17" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2440,34 +2445,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>597477</v>
+        <v>597505</v>
       </c>
       <c r="R17" t="n">
-        <v>6925984</v>
+        <v>6925873</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2499,7 +2509,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2509,7 +2519,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2536,10 +2551,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125066707</v>
+        <v>125069232</v>
       </c>
       <c r="B18" t="n">
-        <v>57995</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2552,39 +2567,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103018</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>597609</v>
+        <v>597507</v>
       </c>
       <c r="R18" t="n">
-        <v>6925861</v>
+        <v>6925959</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2616,7 +2626,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2626,7 +2636,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2653,10 +2663,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125067046</v>
+        <v>125073504</v>
       </c>
       <c r="B19" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2665,43 +2675,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Mpd</t>
+          <t>Svarttjärnsåsen, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>597572</v>
+        <v>597276</v>
       </c>
       <c r="R19" t="n">
-        <v>6925829</v>
+        <v>6926060</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2733,7 +2743,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2743,7 +2753,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2770,10 +2785,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125067179</v>
+        <v>125067552</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2786,39 +2801,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>597556</v>
+        <v>597549</v>
       </c>
       <c r="R20" t="n">
-        <v>6925836</v>
+        <v>6925866</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2850,7 +2860,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2860,12 +2870,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:07</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2892,10 +2897,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125067365</v>
+        <v>125067837</v>
       </c>
       <c r="B21" t="n">
-        <v>96979</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2904,25 +2909,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2932,10 +2937,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>597572</v>
+        <v>597505</v>
       </c>
       <c r="R21" t="n">
-        <v>6925875</v>
+        <v>6925873</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2967,7 +2972,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2977,7 +2982,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3004,7 +3009,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125071236</v>
+        <v>125067179</v>
       </c>
       <c r="B22" t="n">
         <v>57513</v>
@@ -3049,10 +3054,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>597394</v>
+        <v>597556</v>
       </c>
       <c r="R22" t="n">
-        <v>6926034</v>
+        <v>6925836</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3084,7 +3089,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3094,7 +3099,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3126,10 +3131,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125067837</v>
+        <v>125066963</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3142,21 +3147,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3166,10 +3171,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>597505</v>
+        <v>597575</v>
       </c>
       <c r="R23" t="n">
-        <v>6925873</v>
+        <v>6925842</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3201,7 +3206,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3211,7 +3216,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3238,10 +3243,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125071663</v>
+        <v>125066674</v>
       </c>
       <c r="B24" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3254,16 +3259,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3279,14 +3284,14 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Svarttjärnsåsen, Mpd</t>
+          <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>597242</v>
+        <v>597627</v>
       </c>
       <c r="R24" t="n">
-        <v>6926157</v>
+        <v>6925859</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3318,7 +3323,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3328,7 +3333,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>08:39</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3355,10 +3365,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125067738</v>
+        <v>125073564</v>
       </c>
       <c r="B25" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3371,39 +3381,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Mpd</t>
+          <t>Svarttjärnsåsen, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>597512</v>
+        <v>597336</v>
       </c>
       <c r="R25" t="n">
-        <v>6925861</v>
+        <v>6926029</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3435,7 +3440,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3445,12 +3450,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:28</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3477,7 +3477,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125068606</v>
+        <v>125067046</v>
       </c>
       <c r="B26" t="n">
         <v>56722</v>
@@ -3522,10 +3522,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>597492</v>
+        <v>597572</v>
       </c>
       <c r="R26" t="n">
-        <v>6925938</v>
+        <v>6925829</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3557,7 +3557,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3594,10 +3594,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125070603</v>
+        <v>125070329</v>
       </c>
       <c r="B27" t="n">
-        <v>96979</v>
+        <v>91012</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3606,25 +3606,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>597467</v>
+        <v>597477</v>
       </c>
       <c r="R27" t="n">
-        <v>6925971</v>
+        <v>6925984</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 48961-2024 artfynd.xlsx
+++ b/artfynd/A 48961-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125071236</v>
+        <v>125066854</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597394</v>
+        <v>597598</v>
       </c>
       <c r="R2" t="n">
-        <v>6926034</v>
+        <v>6925850</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125067365</v>
+        <v>125067330</v>
       </c>
       <c r="B3" t="n">
-        <v>96979</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,25 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -872,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125070603</v>
+        <v>125067552</v>
       </c>
       <c r="B4" t="n">
-        <v>96979</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,25 +915,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597467</v>
+        <v>597549</v>
       </c>
       <c r="R4" t="n">
-        <v>6925971</v>
+        <v>6925866</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125068606</v>
+        <v>125066963</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
+        <v>91012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,43 +1027,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597492</v>
+        <v>597575</v>
       </c>
       <c r="R5" t="n">
-        <v>6925938</v>
+        <v>6925842</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,7 +1127,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125069753</v>
+        <v>125067837</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1178,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597481</v>
+        <v>597505</v>
       </c>
       <c r="R6" t="n">
-        <v>6926022</v>
+        <v>6925873</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125071368</v>
+        <v>125071663</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,34 +1255,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Svarttjärnsåsen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597351</v>
+        <v>597242</v>
       </c>
       <c r="R7" t="n">
-        <v>6926064</v>
+        <v>6926157</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1329,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,10 +1356,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125069803</v>
+        <v>125067179</v>
       </c>
       <c r="B8" t="n">
-        <v>56714</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,16 +1372,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1398,7 +1392,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1407,10 +1401,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597481</v>
+        <v>597556</v>
       </c>
       <c r="R8" t="n">
-        <v>6926022</v>
+        <v>6925836</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,7 +1436,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1446,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125067330</v>
+        <v>125070762</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,34 +1494,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597572</v>
+        <v>597398</v>
       </c>
       <c r="R9" t="n">
-        <v>6925875</v>
+        <v>6925953</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,7 +1558,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1568,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,10 +1600,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125066707</v>
+        <v>125067926</v>
       </c>
       <c r="B10" t="n">
-        <v>57995</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,27 +1616,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103018</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1636,10 +1645,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597609</v>
+        <v>597505</v>
       </c>
       <c r="R10" t="n">
-        <v>6925861</v>
+        <v>6925873</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1671,7 +1680,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1681,7 +1690,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1708,10 +1722,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125071010</v>
+        <v>125071368</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1724,39 +1738,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Mpd</t>
+          <t>Svarttjärnsåsen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597422</v>
+        <v>597351</v>
       </c>
       <c r="R11" t="n">
-        <v>6925982</v>
+        <v>6926064</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,7 +1797,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1798,12 +1807,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1830,10 +1834,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125071663</v>
+        <v>125067738</v>
       </c>
       <c r="B12" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1846,16 +1850,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1871,14 +1875,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Svarttjärnsåsen, Mpd</t>
+          <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597242</v>
+        <v>597512</v>
       </c>
       <c r="R12" t="n">
-        <v>6926157</v>
+        <v>6925861</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1910,7 +1914,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1920,7 +1924,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1947,10 +1956,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125066854</v>
+        <v>125071010</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1959,30 +1968,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1991,10 +2001,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>597598</v>
+        <v>597422</v>
       </c>
       <c r="R13" t="n">
-        <v>6925850</v>
+        <v>6925982</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2026,7 +2036,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2036,7 +2046,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2063,10 +2078,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125070762</v>
+        <v>125067046</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2075,31 +2090,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2108,10 +2123,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>597398</v>
+        <v>597572</v>
       </c>
       <c r="R14" t="n">
-        <v>6925953</v>
+        <v>6925829</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2143,7 +2158,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2153,12 +2168,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:04</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2185,10 +2195,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125067738</v>
+        <v>125069753</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2201,39 +2211,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>597512</v>
+        <v>597481</v>
       </c>
       <c r="R15" t="n">
-        <v>6925861</v>
+        <v>6926022</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2265,7 +2270,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2275,12 +2280,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:28</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2307,10 +2307,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125068260</v>
+        <v>125067365</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>96979</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2319,43 +2319,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>597492</v>
+        <v>597572</v>
       </c>
       <c r="R16" t="n">
-        <v>6925938</v>
+        <v>6925875</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2387,7 +2382,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2397,12 +2392,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:55</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2429,7 +2419,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125067978</v>
+        <v>125068260</v>
       </c>
       <c r="B17" t="n">
         <v>57513</v>
@@ -2474,10 +2464,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>597505</v>
+        <v>597492</v>
       </c>
       <c r="R17" t="n">
-        <v>6925873</v>
+        <v>6925938</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2509,7 +2499,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2519,7 +2509,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2551,10 +2541,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125069232</v>
+        <v>125066707</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>57995</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2567,34 +2557,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>103018</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>597507</v>
+        <v>597609</v>
       </c>
       <c r="R18" t="n">
-        <v>6925959</v>
+        <v>6925861</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2626,7 +2621,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2636,7 +2631,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2663,10 +2658,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125073504</v>
+        <v>125069232</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2679,39 +2674,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Svarttjärnsåsen, Mpd</t>
+          <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>597276</v>
+        <v>597507</v>
       </c>
       <c r="R19" t="n">
-        <v>6926060</v>
+        <v>6925959</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2743,7 +2733,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2753,12 +2743,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2785,10 +2770,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125067552</v>
+        <v>125069803</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2801,34 +2786,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>597549</v>
+        <v>597481</v>
       </c>
       <c r="R20" t="n">
-        <v>6925866</v>
+        <v>6926022</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2860,7 +2850,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2870,7 +2860,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2897,10 +2887,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125067837</v>
+        <v>125068606</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2909,38 +2899,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>597505</v>
+        <v>597492</v>
       </c>
       <c r="R21" t="n">
-        <v>6925873</v>
+        <v>6925938</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2972,7 +2967,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2982,7 +2977,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3009,7 +3004,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125067179</v>
+        <v>125071236</v>
       </c>
       <c r="B22" t="n">
         <v>57513</v>
@@ -3054,10 +3049,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>597556</v>
+        <v>597394</v>
       </c>
       <c r="R22" t="n">
-        <v>6925836</v>
+        <v>6926034</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3089,7 +3084,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3099,7 +3094,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3131,7 +3126,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125066963</v>
+        <v>125070329</v>
       </c>
       <c r="B23" t="n">
         <v>91012</v>
@@ -3171,10 +3166,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>597575</v>
+        <v>597477</v>
       </c>
       <c r="R23" t="n">
-        <v>6925842</v>
+        <v>6925984</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3206,7 +3201,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3216,7 +3211,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3243,10 +3238,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125066674</v>
+        <v>125073564</v>
       </c>
       <c r="B24" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3259,39 +3254,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Mpd</t>
+          <t>Svarttjärnsåsen, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>597627</v>
+        <v>597336</v>
       </c>
       <c r="R24" t="n">
-        <v>6925859</v>
+        <v>6926029</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3323,7 +3313,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3333,12 +3323,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>08:39</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3365,10 +3350,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125073564</v>
+        <v>125066674</v>
       </c>
       <c r="B25" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3381,34 +3366,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Svarttjärnsåsen, Mpd</t>
+          <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>597336</v>
+        <v>597627</v>
       </c>
       <c r="R25" t="n">
-        <v>6926029</v>
+        <v>6925859</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3440,7 +3430,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3450,7 +3440,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>08:39</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3477,10 +3472,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125067046</v>
+        <v>125073504</v>
       </c>
       <c r="B26" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3489,43 +3484,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Mpd</t>
+          <t>Svarttjärnsåsen, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>597572</v>
+        <v>597276</v>
       </c>
       <c r="R26" t="n">
-        <v>6925829</v>
+        <v>6926060</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3557,7 +3552,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3567,7 +3562,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3594,10 +3594,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125070329</v>
+        <v>125070603</v>
       </c>
       <c r="B27" t="n">
-        <v>91012</v>
+        <v>96979</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3606,25 +3606,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>597477</v>
+        <v>597467</v>
       </c>
       <c r="R27" t="n">
-        <v>6925984</v>
+        <v>6925971</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 48961-2024 artfynd.xlsx
+++ b/artfynd/A 48961-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125066854</v>
+        <v>125067330</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597598</v>
+        <v>597572</v>
       </c>
       <c r="R2" t="n">
-        <v>6925850</v>
+        <v>6925875</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125067330</v>
+        <v>125067552</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -831,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597572</v>
+        <v>597549</v>
       </c>
       <c r="R3" t="n">
-        <v>6925875</v>
+        <v>6925866</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125067552</v>
+        <v>125066854</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,38 +911,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597549</v>
+        <v>597598</v>
       </c>
       <c r="R4" t="n">
-        <v>6925866</v>
+        <v>6925850</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -2887,10 +2887,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125068606</v>
+        <v>125071236</v>
       </c>
       <c r="B21" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2899,31 +2899,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>597492</v>
+        <v>597394</v>
       </c>
       <c r="R21" t="n">
-        <v>6925938</v>
+        <v>6926034</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2977,7 +2977,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3004,10 +3009,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125071236</v>
+        <v>125068606</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3016,31 +3021,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3049,10 +3054,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>597394</v>
+        <v>597492</v>
       </c>
       <c r="R22" t="n">
-        <v>6926034</v>
+        <v>6925938</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3084,7 +3089,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3094,12 +3099,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3350,10 +3350,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125066674</v>
+        <v>125070603</v>
       </c>
       <c r="B25" t="n">
-        <v>57513</v>
+        <v>96979</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3362,43 +3362,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>597627</v>
+        <v>597467</v>
       </c>
       <c r="R25" t="n">
-        <v>6925859</v>
+        <v>6925971</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3430,7 +3425,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3440,12 +3435,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>08:39</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3472,7 +3462,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125073504</v>
+        <v>125066674</v>
       </c>
       <c r="B26" t="n">
         <v>57513</v>
@@ -3508,19 +3498,19 @@
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Svarttjärnsåsen, Mpd</t>
+          <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>597276</v>
+        <v>597627</v>
       </c>
       <c r="R26" t="n">
-        <v>6926060</v>
+        <v>6925859</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3552,7 +3542,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3562,12 +3552,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3594,10 +3584,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125070603</v>
+        <v>125073504</v>
       </c>
       <c r="B27" t="n">
-        <v>96979</v>
+        <v>57513</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3606,38 +3596,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Mpd</t>
+          <t>Svarttjärnsåsen, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>597467</v>
+        <v>597276</v>
       </c>
       <c r="R27" t="n">
-        <v>6925971</v>
+        <v>6926060</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3669,7 +3664,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3679,7 +3674,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 48961-2024 artfynd.xlsx
+++ b/artfynd/A 48961-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125067330</v>
+        <v>125066854</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597572</v>
+        <v>597598</v>
       </c>
       <c r="R2" t="n">
-        <v>6925875</v>
+        <v>6925850</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125067552</v>
+        <v>125067330</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -827,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597549</v>
+        <v>597572</v>
       </c>
       <c r="R3" t="n">
-        <v>6925866</v>
+        <v>6925875</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125066854</v>
+        <v>125067552</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,42 +915,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597598</v>
+        <v>597549</v>
       </c>
       <c r="R4" t="n">
-        <v>6925850</v>
+        <v>6925866</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -2887,10 +2887,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125071236</v>
+        <v>125068606</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2899,31 +2899,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>597394</v>
+        <v>597492</v>
       </c>
       <c r="R21" t="n">
-        <v>6926034</v>
+        <v>6925938</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2977,12 +2977,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3009,10 +3004,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125068606</v>
+        <v>125071236</v>
       </c>
       <c r="B22" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3021,31 +3016,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3054,10 +3049,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>597492</v>
+        <v>597394</v>
       </c>
       <c r="R22" t="n">
-        <v>6925938</v>
+        <v>6926034</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3089,7 +3084,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3099,7 +3094,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 48961-2024 artfynd.xlsx
+++ b/artfynd/A 48961-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125066854</v>
+        <v>125069753</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597598</v>
+        <v>597481</v>
       </c>
       <c r="R2" t="n">
-        <v>6925850</v>
+        <v>6926022</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125067330</v>
+        <v>125071368</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -827,14 +823,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Mpd</t>
+          <t>Svarttjärnsåsen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597572</v>
+        <v>597351</v>
       </c>
       <c r="R3" t="n">
-        <v>6925875</v>
+        <v>6926064</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125067552</v>
+        <v>125067738</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,34 +915,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597549</v>
+        <v>597512</v>
       </c>
       <c r="R4" t="n">
-        <v>6925866</v>
+        <v>6925861</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125066963</v>
+        <v>125067046</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>56722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,38 +1033,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597575</v>
+        <v>597572</v>
       </c>
       <c r="R5" t="n">
-        <v>6925842</v>
+        <v>6925829</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,7 +1138,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125067837</v>
+        <v>125069232</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1167,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597505</v>
+        <v>597507</v>
       </c>
       <c r="R6" t="n">
-        <v>6925873</v>
+        <v>6925959</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125071663</v>
+        <v>125066854</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,43 +1262,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svarttjärnsåsen, Mpd</t>
+          <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597242</v>
+        <v>597598</v>
       </c>
       <c r="R7" t="n">
-        <v>6926157</v>
+        <v>6925850</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,7 +1329,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,7 +1339,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,7 +1366,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125067179</v>
+        <v>125067926</v>
       </c>
       <c r="B8" t="n">
         <v>57513</v>
@@ -1392,7 +1402,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1401,10 +1411,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597556</v>
+        <v>597505</v>
       </c>
       <c r="R8" t="n">
-        <v>6925836</v>
+        <v>6925873</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1436,7 +1446,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1446,7 +1456,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1478,7 +1488,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125070762</v>
+        <v>125067179</v>
       </c>
       <c r="B9" t="n">
         <v>57513</v>
@@ -1514,7 +1524,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1523,10 +1533,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597398</v>
+        <v>597556</v>
       </c>
       <c r="R9" t="n">
-        <v>6925953</v>
+        <v>6925836</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1558,7 +1568,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1568,7 +1578,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1600,10 +1610,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125067926</v>
+        <v>125067330</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1616,39 +1626,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597505</v>
+        <v>597572</v>
       </c>
       <c r="R10" t="n">
-        <v>6925873</v>
+        <v>6925875</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1680,7 +1685,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1690,12 +1695,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:37</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1722,10 +1722,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125071368</v>
+        <v>125071236</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1738,34 +1738,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Svarttjärnsåsen, Mpd</t>
+          <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597351</v>
+        <v>597394</v>
       </c>
       <c r="R11" t="n">
-        <v>6926064</v>
+        <v>6926034</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1797,7 +1802,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1807,7 +1812,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1834,7 +1844,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125067738</v>
+        <v>125071010</v>
       </c>
       <c r="B12" t="n">
         <v>57513</v>
@@ -1879,10 +1889,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597512</v>
+        <v>597422</v>
       </c>
       <c r="R12" t="n">
-        <v>6925861</v>
+        <v>6925982</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1914,7 +1924,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1924,7 +1934,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1956,7 +1966,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125071010</v>
+        <v>125070762</v>
       </c>
       <c r="B13" t="n">
         <v>57513</v>
@@ -1992,7 +2002,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2001,10 +2011,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>597422</v>
+        <v>597398</v>
       </c>
       <c r="R13" t="n">
-        <v>6925982</v>
+        <v>6925953</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2036,7 +2046,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2046,7 +2056,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2078,10 +2088,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125067046</v>
+        <v>125069803</v>
       </c>
       <c r="B14" t="n">
-        <v>56722</v>
+        <v>56714</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2090,31 +2100,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2123,10 +2133,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>597572</v>
+        <v>597481</v>
       </c>
       <c r="R14" t="n">
-        <v>6925829</v>
+        <v>6926022</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2158,7 +2168,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2168,7 +2178,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2195,10 +2205,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125069753</v>
+        <v>125073504</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2211,34 +2221,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Mpd</t>
+          <t>Svarttjärnsåsen, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>597481</v>
+        <v>597276</v>
       </c>
       <c r="R15" t="n">
-        <v>6926022</v>
+        <v>6926060</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2270,7 +2285,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2280,7 +2295,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2307,10 +2327,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125067365</v>
+        <v>125067552</v>
       </c>
       <c r="B16" t="n">
-        <v>96979</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2319,25 +2339,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2347,10 +2367,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>597572</v>
+        <v>597549</v>
       </c>
       <c r="R16" t="n">
-        <v>6925875</v>
+        <v>6925866</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2382,7 +2402,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2392,7 +2412,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2419,10 +2439,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125068260</v>
+        <v>125068606</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2431,31 +2451,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2499,7 +2519,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2509,12 +2529,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:55</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2541,10 +2556,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125066707</v>
+        <v>125067837</v>
       </c>
       <c r="B18" t="n">
-        <v>57995</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2557,39 +2572,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103018</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>597609</v>
+        <v>597505</v>
       </c>
       <c r="R18" t="n">
-        <v>6925861</v>
+        <v>6925873</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2621,7 +2631,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2631,7 +2641,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2658,10 +2668,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125069232</v>
+        <v>125066963</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2674,21 +2684,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2698,10 +2708,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>597507</v>
+        <v>597575</v>
       </c>
       <c r="R19" t="n">
-        <v>6925959</v>
+        <v>6925842</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2733,7 +2743,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2743,7 +2753,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2770,10 +2780,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125069803</v>
+        <v>125070603</v>
       </c>
       <c r="B20" t="n">
-        <v>56714</v>
+        <v>96979</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2782,43 +2792,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102612</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>597481</v>
+        <v>597467</v>
       </c>
       <c r="R20" t="n">
-        <v>6926022</v>
+        <v>6925971</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2850,7 +2855,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2860,7 +2865,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2887,10 +2892,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125068606</v>
+        <v>125066707</v>
       </c>
       <c r="B21" t="n">
-        <v>56722</v>
+        <v>57995</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2899,31 +2904,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>103018</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2932,10 +2937,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>597492</v>
+        <v>597609</v>
       </c>
       <c r="R21" t="n">
-        <v>6925938</v>
+        <v>6925861</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2967,7 +2972,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2977,7 +2982,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3004,10 +3009,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125071236</v>
+        <v>125070329</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3020,39 +3025,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>597394</v>
+        <v>597477</v>
       </c>
       <c r="R22" t="n">
-        <v>6926034</v>
+        <v>6925984</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3094,12 +3094,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3126,10 +3121,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125070329</v>
+        <v>125073564</v>
       </c>
       <c r="B23" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3142,34 +3137,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Mpd</t>
+          <t>Svarttjärnsåsen, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>597477</v>
+        <v>597336</v>
       </c>
       <c r="R23" t="n">
-        <v>6925984</v>
+        <v>6926029</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3201,7 +3196,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3211,7 +3206,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3238,10 +3233,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125073564</v>
+        <v>125067365</v>
       </c>
       <c r="B24" t="n">
-        <v>79891</v>
+        <v>96979</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3250,38 +3245,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Svarttjärnsåsen, Mpd</t>
+          <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>597336</v>
+        <v>597572</v>
       </c>
       <c r="R24" t="n">
-        <v>6926029</v>
+        <v>6925875</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3313,7 +3308,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3323,7 +3318,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3350,10 +3345,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125070603</v>
+        <v>125066674</v>
       </c>
       <c r="B25" t="n">
-        <v>96979</v>
+        <v>57513</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3362,38 +3357,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>597467</v>
+        <v>597627</v>
       </c>
       <c r="R25" t="n">
-        <v>6925971</v>
+        <v>6925859</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3425,7 +3425,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3435,7 +3435,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>08:39</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3462,7 +3467,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125066674</v>
+        <v>125068260</v>
       </c>
       <c r="B26" t="n">
         <v>57513</v>
@@ -3507,10 +3512,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>597627</v>
+        <v>597492</v>
       </c>
       <c r="R26" t="n">
-        <v>6925859</v>
+        <v>6925938</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3542,7 +3547,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3552,12 +3557,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3584,10 +3589,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125073504</v>
+        <v>125071663</v>
       </c>
       <c r="B27" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3600,16 +3605,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3620,7 +3625,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3629,10 +3634,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>597276</v>
+        <v>597242</v>
       </c>
       <c r="R27" t="n">
-        <v>6926060</v>
+        <v>6926157</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3664,7 +3669,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3674,12 +3679,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 48961-2024 artfynd.xlsx
+++ b/artfynd/A 48961-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125069753</v>
+        <v>125067365</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>96979</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597481</v>
+        <v>597572</v>
       </c>
       <c r="R2" t="n">
-        <v>6926022</v>
+        <v>6925875</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125071368</v>
+        <v>125067738</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svarttjärnsåsen, Mpd</t>
+          <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597351</v>
+        <v>597512</v>
       </c>
       <c r="R3" t="n">
-        <v>6926064</v>
+        <v>6925861</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125067738</v>
+        <v>125067837</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,39 +925,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597512</v>
+        <v>597505</v>
       </c>
       <c r="R4" t="n">
-        <v>6925861</v>
+        <v>6925873</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:28</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125067046</v>
+        <v>125071236</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,31 +1033,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597572</v>
+        <v>597394</v>
       </c>
       <c r="R5" t="n">
-        <v>6925829</v>
+        <v>6926034</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1111,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,7 +1143,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125069232</v>
+        <v>125067552</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1178,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597507</v>
+        <v>597549</v>
       </c>
       <c r="R6" t="n">
-        <v>6925959</v>
+        <v>6925866</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125066854</v>
+        <v>125071010</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,30 +1267,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1294,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597598</v>
+        <v>597422</v>
       </c>
       <c r="R7" t="n">
-        <v>6925850</v>
+        <v>6925982</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1339,7 +1345,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125067926</v>
+        <v>125069753</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,39 +1393,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597505</v>
+        <v>597481</v>
       </c>
       <c r="R8" t="n">
-        <v>6925873</v>
+        <v>6926022</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1446,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,12 +1462,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:37</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,10 +1489,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125067179</v>
+        <v>125069803</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>56714</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1504,16 +1505,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1524,7 +1525,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1533,10 +1534,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597556</v>
+        <v>597481</v>
       </c>
       <c r="R9" t="n">
-        <v>6925836</v>
+        <v>6926022</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1568,7 +1569,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1578,12 +1579,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:07</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1610,7 +1606,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125067330</v>
+        <v>125071368</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1646,14 +1642,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Mpd</t>
+          <t>Svarttjärnsåsen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597572</v>
+        <v>597351</v>
       </c>
       <c r="R10" t="n">
-        <v>6925875</v>
+        <v>6926064</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1685,7 +1681,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1695,7 +1691,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1722,10 +1718,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125071236</v>
+        <v>125067330</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1738,39 +1734,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597394</v>
+        <v>597572</v>
       </c>
       <c r="R11" t="n">
-        <v>6926034</v>
+        <v>6925875</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1802,7 +1793,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1812,12 +1803,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1844,10 +1830,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125071010</v>
+        <v>125068606</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1856,31 +1842,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1889,10 +1875,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597422</v>
+        <v>597492</v>
       </c>
       <c r="R12" t="n">
-        <v>6925982</v>
+        <v>6925938</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1924,7 +1910,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1934,12 +1920,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1966,10 +1947,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125070762</v>
+        <v>125066854</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1978,31 +1959,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2011,10 +1991,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>597398</v>
+        <v>597598</v>
       </c>
       <c r="R13" t="n">
-        <v>6925953</v>
+        <v>6925850</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2046,7 +2026,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2056,12 +2036,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:04</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2088,10 +2063,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125069803</v>
+        <v>125070603</v>
       </c>
       <c r="B14" t="n">
-        <v>56714</v>
+        <v>96979</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2100,43 +2075,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>597481</v>
+        <v>597467</v>
       </c>
       <c r="R14" t="n">
-        <v>6926022</v>
+        <v>6925971</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2168,7 +2138,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2178,7 +2148,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2205,7 +2175,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125073504</v>
+        <v>125070762</v>
       </c>
       <c r="B15" t="n">
         <v>57513</v>
@@ -2246,14 +2216,14 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Svarttjärnsåsen, Mpd</t>
+          <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>597276</v>
+        <v>597398</v>
       </c>
       <c r="R15" t="n">
-        <v>6926060</v>
+        <v>6925953</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2285,7 +2255,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2295,7 +2265,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2327,10 +2297,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125067552</v>
+        <v>125066963</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2343,21 +2313,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2367,10 +2337,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>597549</v>
+        <v>597575</v>
       </c>
       <c r="R16" t="n">
-        <v>6925866</v>
+        <v>6925842</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2402,7 +2372,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2412,7 +2382,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2439,10 +2409,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125068606</v>
+        <v>125070329</v>
       </c>
       <c r="B17" t="n">
-        <v>56722</v>
+        <v>91012</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2451,43 +2421,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>597492</v>
+        <v>597477</v>
       </c>
       <c r="R17" t="n">
-        <v>6925938</v>
+        <v>6925984</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2519,7 +2484,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2529,7 +2494,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2556,10 +2521,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125067837</v>
+        <v>125073564</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2572,34 +2537,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Mpd</t>
+          <t>Svarttjärnsåsen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>597505</v>
+        <v>597336</v>
       </c>
       <c r="R18" t="n">
-        <v>6925873</v>
+        <v>6926029</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2631,7 +2596,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2641,7 +2606,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2668,10 +2633,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125066963</v>
+        <v>125067978</v>
       </c>
       <c r="B19" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2684,34 +2649,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>597575</v>
+        <v>597505</v>
       </c>
       <c r="R19" t="n">
-        <v>6925842</v>
+        <v>6925873</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2743,7 +2713,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2753,7 +2723,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2780,10 +2755,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125070603</v>
+        <v>125068260</v>
       </c>
       <c r="B20" t="n">
-        <v>96979</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2792,38 +2767,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>597467</v>
+        <v>597492</v>
       </c>
       <c r="R20" t="n">
-        <v>6925971</v>
+        <v>6925938</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2855,7 +2835,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2865,7 +2845,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2892,10 +2877,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125066707</v>
+        <v>125067046</v>
       </c>
       <c r="B21" t="n">
-        <v>57995</v>
+        <v>56722</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2904,31 +2889,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103018</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2937,10 +2922,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>597609</v>
+        <v>597572</v>
       </c>
       <c r="R21" t="n">
-        <v>6925861</v>
+        <v>6925829</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2972,7 +2957,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2982,7 +2967,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3009,10 +2994,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125070329</v>
+        <v>125073504</v>
       </c>
       <c r="B22" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3025,34 +3010,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Mpd</t>
+          <t>Svarttjärnsåsen, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>597477</v>
+        <v>597276</v>
       </c>
       <c r="R22" t="n">
-        <v>6925984</v>
+        <v>6926060</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3084,7 +3074,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3094,7 +3084,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3121,10 +3116,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125073564</v>
+        <v>125071663</v>
       </c>
       <c r="B23" t="n">
-        <v>79891</v>
+        <v>57529</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3137,34 +3132,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Svarttjärnsåsen, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>597336</v>
+        <v>597242</v>
       </c>
       <c r="R23" t="n">
-        <v>6926029</v>
+        <v>6926157</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3233,10 +3233,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125067365</v>
+        <v>125066674</v>
       </c>
       <c r="B24" t="n">
-        <v>96979</v>
+        <v>57513</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3245,38 +3245,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>597572</v>
+        <v>597627</v>
       </c>
       <c r="R24" t="n">
-        <v>6925875</v>
+        <v>6925859</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3308,7 +3313,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3318,7 +3323,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:39</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3345,10 +3355,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125066674</v>
+        <v>125066707</v>
       </c>
       <c r="B25" t="n">
-        <v>57513</v>
+        <v>57995</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3361,27 +3371,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>103018</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3390,10 +3400,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>597627</v>
+        <v>597609</v>
       </c>
       <c r="R25" t="n">
-        <v>6925859</v>
+        <v>6925861</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3425,7 +3435,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3435,12 +3445,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>08:39</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3467,7 +3472,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125068260</v>
+        <v>125067179</v>
       </c>
       <c r="B26" t="n">
         <v>57513</v>
@@ -3512,10 +3517,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>597492</v>
+        <v>597556</v>
       </c>
       <c r="R26" t="n">
-        <v>6925938</v>
+        <v>6925836</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3547,7 +3552,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3557,7 +3562,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3589,10 +3594,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125071663</v>
+        <v>125069232</v>
       </c>
       <c r="B27" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3605,39 +3610,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Svarttjärnsåsen, Mpd</t>
+          <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>597242</v>
+        <v>597507</v>
       </c>
       <c r="R27" t="n">
-        <v>6926157</v>
+        <v>6925959</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 48961-2024 artfynd.xlsx
+++ b/artfynd/A 48961-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125067365</v>
+        <v>125070329</v>
       </c>
       <c r="B2" t="n">
-        <v>96979</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597572</v>
+        <v>597477</v>
       </c>
       <c r="R2" t="n">
-        <v>6925875</v>
+        <v>6925984</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125067738</v>
+        <v>125069753</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597512</v>
+        <v>597481</v>
       </c>
       <c r="R3" t="n">
-        <v>6925861</v>
+        <v>6926022</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:28</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125067837</v>
+        <v>125066707</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>57995</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,34 +915,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>103018</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597505</v>
+        <v>597609</v>
       </c>
       <c r="R4" t="n">
-        <v>6925873</v>
+        <v>6925861</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,7 +1016,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125071236</v>
+        <v>125066674</v>
       </c>
       <c r="B5" t="n">
         <v>57513</v>
@@ -1066,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597394</v>
+        <v>597627</v>
       </c>
       <c r="R5" t="n">
-        <v>6926034</v>
+        <v>6925859</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,12 +1106,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125067552</v>
+        <v>125067365</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>96979</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,25 +1150,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597549</v>
+        <v>597572</v>
       </c>
       <c r="R6" t="n">
-        <v>6925866</v>
+        <v>6925875</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125071010</v>
+        <v>125067837</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,39 +1266,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597422</v>
+        <v>597505</v>
       </c>
       <c r="R7" t="n">
-        <v>6925982</v>
+        <v>6925873</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,12 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125069753</v>
+        <v>125067046</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1389,38 +1374,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597481</v>
+        <v>597572</v>
       </c>
       <c r="R8" t="n">
-        <v>6926022</v>
+        <v>6925829</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1462,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1489,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125069803</v>
+        <v>125071368</v>
       </c>
       <c r="B9" t="n">
-        <v>56714</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1505,39 +1495,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Mpd</t>
+          <t>Svarttjärnsåsen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597481</v>
+        <v>597351</v>
       </c>
       <c r="R9" t="n">
-        <v>6926022</v>
+        <v>6926064</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1569,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1579,7 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1606,10 +1591,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125071368</v>
+        <v>125073504</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1622,34 +1607,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Svarttjärnsåsen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597351</v>
+        <v>597276</v>
       </c>
       <c r="R10" t="n">
-        <v>6926064</v>
+        <v>6926060</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1681,7 +1671,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1691,7 +1681,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1718,10 +1713,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125067330</v>
+        <v>125067978</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1734,34 +1729,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597572</v>
+        <v>597505</v>
       </c>
       <c r="R11" t="n">
-        <v>6925875</v>
+        <v>6925873</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1803,7 +1803,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1830,10 +1835,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125068606</v>
+        <v>125069232</v>
       </c>
       <c r="B12" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1842,43 +1847,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597492</v>
+        <v>597507</v>
       </c>
       <c r="R12" t="n">
-        <v>6925938</v>
+        <v>6925959</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1947,10 +1947,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125066854</v>
+        <v>125070762</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1959,30 +1959,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1991,10 +1992,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>597598</v>
+        <v>597398</v>
       </c>
       <c r="R13" t="n">
-        <v>6925850</v>
+        <v>6925953</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2026,7 +2027,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2036,7 +2037,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2063,10 +2069,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125070603</v>
+        <v>125071010</v>
       </c>
       <c r="B14" t="n">
-        <v>96979</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2075,38 +2081,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>597467</v>
+        <v>597422</v>
       </c>
       <c r="R14" t="n">
-        <v>6925971</v>
+        <v>6925982</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2138,7 +2149,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2148,7 +2159,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2175,10 +2191,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125070762</v>
+        <v>125066963</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2191,39 +2207,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>597398</v>
+        <v>597575</v>
       </c>
       <c r="R15" t="n">
-        <v>6925953</v>
+        <v>6925842</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2255,7 +2266,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2265,12 +2276,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:04</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2297,10 +2303,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125066963</v>
+        <v>125069803</v>
       </c>
       <c r="B16" t="n">
-        <v>91012</v>
+        <v>56714</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2313,34 +2319,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>597575</v>
+        <v>597481</v>
       </c>
       <c r="R16" t="n">
-        <v>6925842</v>
+        <v>6926022</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2372,7 +2383,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2382,7 +2393,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2409,10 +2420,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125070329</v>
+        <v>125068260</v>
       </c>
       <c r="B17" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2425,34 +2436,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>597477</v>
+        <v>597492</v>
       </c>
       <c r="R17" t="n">
-        <v>6925984</v>
+        <v>6925938</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2484,7 +2500,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2494,7 +2510,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2521,10 +2542,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125073564</v>
+        <v>125071236</v>
       </c>
       <c r="B18" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2537,34 +2558,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Svarttjärnsåsen, Mpd</t>
+          <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>597336</v>
+        <v>597394</v>
       </c>
       <c r="R18" t="n">
-        <v>6926029</v>
+        <v>6926034</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2596,7 +2622,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2606,7 +2632,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2633,7 +2664,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125067978</v>
+        <v>125067179</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -2678,10 +2709,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>597505</v>
+        <v>597556</v>
       </c>
       <c r="R19" t="n">
-        <v>6925873</v>
+        <v>6925836</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2713,7 +2744,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2723,7 +2754,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2755,10 +2786,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125068260</v>
+        <v>125068606</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2767,31 +2798,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2835,7 +2866,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2845,12 +2876,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:55</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2877,10 +2903,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125067046</v>
+        <v>125067330</v>
       </c>
       <c r="B21" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2889,33 +2915,28 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
@@ -2925,7 +2946,7 @@
         <v>597572</v>
       </c>
       <c r="R21" t="n">
-        <v>6925829</v>
+        <v>6925875</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2957,7 +2978,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2967,7 +2988,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2994,10 +3015,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125073504</v>
+        <v>125071663</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3010,16 +3031,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3030,7 +3051,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3039,10 +3060,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>597276</v>
+        <v>597242</v>
       </c>
       <c r="R22" t="n">
-        <v>6926060</v>
+        <v>6926157</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3074,7 +3095,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3084,12 +3105,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3116,10 +3132,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125071663</v>
+        <v>125067552</v>
       </c>
       <c r="B23" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3132,39 +3148,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Svarttjärnsåsen, Mpd</t>
+          <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>597242</v>
+        <v>597549</v>
       </c>
       <c r="R23" t="n">
-        <v>6926157</v>
+        <v>6925866</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3196,7 +3207,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3206,7 +3217,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3233,10 +3244,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125066674</v>
+        <v>125073564</v>
       </c>
       <c r="B24" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3249,39 +3260,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Mpd</t>
+          <t>Svarttjärnsåsen, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>597627</v>
+        <v>597336</v>
       </c>
       <c r="R24" t="n">
-        <v>6925859</v>
+        <v>6926029</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3313,7 +3319,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3323,12 +3329,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>08:39</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3355,10 +3356,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125066707</v>
+        <v>125067738</v>
       </c>
       <c r="B25" t="n">
-        <v>57995</v>
+        <v>57513</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3371,27 +3372,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103018</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3400,7 +3401,7 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>597609</v>
+        <v>597512</v>
       </c>
       <c r="R25" t="n">
         <v>6925861</v>
@@ -3435,7 +3436,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3445,7 +3446,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3472,10 +3478,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125067179</v>
+        <v>125070603</v>
       </c>
       <c r="B26" t="n">
-        <v>57513</v>
+        <v>96979</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3484,43 +3490,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>597556</v>
+        <v>597467</v>
       </c>
       <c r="R26" t="n">
-        <v>6925836</v>
+        <v>6925971</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3552,7 +3553,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3562,12 +3563,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:07</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3594,10 +3590,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125069232</v>
+        <v>125066854</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3606,38 +3602,42 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>597507</v>
+        <v>597598</v>
       </c>
       <c r="R27" t="n">
-        <v>6925959</v>
+        <v>6925850</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 48961-2024 artfynd.xlsx
+++ b/artfynd/A 48961-2024 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125069753</v>
+        <v>125066674</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597481</v>
+        <v>597627</v>
       </c>
       <c r="R3" t="n">
-        <v>6926022</v>
+        <v>6925859</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>08:39</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1016,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125066674</v>
+        <v>125069753</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,39 +1042,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597627</v>
+        <v>597481</v>
       </c>
       <c r="R5" t="n">
-        <v>6925859</v>
+        <v>6926022</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,12 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:39</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 48961-2024 artfynd.xlsx
+++ b/artfynd/A 48961-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125070329</v>
+        <v>125073504</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Mpd</t>
+          <t>Svarttjärnsåsen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597477</v>
+        <v>597276</v>
       </c>
       <c r="R2" t="n">
-        <v>6925984</v>
+        <v>6926060</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +797,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125066674</v>
+        <v>125067978</v>
       </c>
       <c r="B3" t="n">
         <v>57513</v>
@@ -832,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597627</v>
+        <v>597505</v>
       </c>
       <c r="R3" t="n">
-        <v>6925859</v>
+        <v>6925873</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +887,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125066707</v>
+        <v>125073564</v>
       </c>
       <c r="B4" t="n">
-        <v>57995</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,39 +935,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103018</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Mpd</t>
+          <t>Svarttjärnsåsen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597609</v>
+        <v>597336</v>
       </c>
       <c r="R4" t="n">
-        <v>6925861</v>
+        <v>6926029</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,7 +1031,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125069753</v>
+        <v>125069232</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1066,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597481</v>
+        <v>597507</v>
       </c>
       <c r="R5" t="n">
-        <v>6926022</v>
+        <v>6925959</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1116,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125067365</v>
+        <v>125067330</v>
       </c>
       <c r="B6" t="n">
-        <v>96979</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,25 +1155,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1213,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125067837</v>
+        <v>125067046</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,38 +1267,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597505</v>
+        <v>597572</v>
       </c>
       <c r="R7" t="n">
-        <v>6925873</v>
+        <v>6925829</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1345,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125067046</v>
+        <v>125066854</v>
       </c>
       <c r="B8" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,31 +1384,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1407,10 +1416,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597572</v>
+        <v>597598</v>
       </c>
       <c r="R8" t="n">
-        <v>6925829</v>
+        <v>6925850</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,7 +1451,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1461,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,10 +1488,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125071368</v>
+        <v>125066674</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,34 +1504,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svarttjärnsåsen, Mpd</t>
+          <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597351</v>
+        <v>597627</v>
       </c>
       <c r="R9" t="n">
-        <v>6926064</v>
+        <v>6925859</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,7 +1568,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1578,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>08:39</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,10 +1610,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125073504</v>
+        <v>125070603</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>96979</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1603,43 +1622,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Svarttjärnsåsen, Mpd</t>
+          <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597276</v>
+        <v>597467</v>
       </c>
       <c r="R10" t="n">
-        <v>6926060</v>
+        <v>6925971</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1671,7 +1685,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1681,12 +1695,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1713,7 +1722,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125067978</v>
+        <v>125068260</v>
       </c>
       <c r="B11" t="n">
         <v>57513</v>
@@ -1758,10 +1767,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597505</v>
+        <v>597492</v>
       </c>
       <c r="R11" t="n">
-        <v>6925873</v>
+        <v>6925938</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1793,7 +1802,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1803,7 +1812,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1835,10 +1844,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125069232</v>
+        <v>125067738</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1851,34 +1860,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597507</v>
+        <v>597512</v>
       </c>
       <c r="R12" t="n">
-        <v>6925959</v>
+        <v>6925861</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1910,7 +1924,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1920,7 +1934,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1947,10 +1966,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125070762</v>
+        <v>125070329</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1963,39 +1982,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>597398</v>
+        <v>597477</v>
       </c>
       <c r="R13" t="n">
-        <v>6925953</v>
+        <v>6925984</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2027,7 +2041,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2037,12 +2051,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:04</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2069,10 +2078,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125071010</v>
+        <v>125071663</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2085,16 +2094,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2110,14 +2119,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Mpd</t>
+          <t>Svarttjärnsåsen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>597422</v>
+        <v>597242</v>
       </c>
       <c r="R14" t="n">
-        <v>6925982</v>
+        <v>6926157</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2149,7 +2158,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2159,12 +2168,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2191,10 +2195,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125066963</v>
+        <v>125067552</v>
       </c>
       <c r="B15" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2207,21 +2211,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2231,10 +2235,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>597575</v>
+        <v>597549</v>
       </c>
       <c r="R15" t="n">
-        <v>6925842</v>
+        <v>6925866</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2266,7 +2270,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2276,7 +2280,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2303,10 +2307,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125069803</v>
+        <v>125068606</v>
       </c>
       <c r="B16" t="n">
-        <v>56714</v>
+        <v>56722</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2315,31 +2319,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2348,10 +2352,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>597481</v>
+        <v>597492</v>
       </c>
       <c r="R16" t="n">
-        <v>6926022</v>
+        <v>6925938</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2383,7 +2387,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2393,7 +2397,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2420,10 +2424,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125068260</v>
+        <v>125069803</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>56714</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2436,16 +2440,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2456,7 +2460,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2465,10 +2469,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>597492</v>
+        <v>597481</v>
       </c>
       <c r="R17" t="n">
-        <v>6925938</v>
+        <v>6926022</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2500,7 +2504,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2510,12 +2514,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:55</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2542,10 +2541,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125071236</v>
+        <v>125066707</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>57995</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2558,27 +2557,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>103018</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2587,10 +2586,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>597394</v>
+        <v>597609</v>
       </c>
       <c r="R18" t="n">
-        <v>6926034</v>
+        <v>6925861</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2622,7 +2621,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2632,12 +2631,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2664,10 +2658,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125067179</v>
+        <v>125069753</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2680,39 +2674,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>597556</v>
+        <v>597481</v>
       </c>
       <c r="R19" t="n">
-        <v>6925836</v>
+        <v>6926022</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2744,7 +2733,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2754,12 +2743,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:07</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2786,10 +2770,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125068606</v>
+        <v>125067179</v>
       </c>
       <c r="B20" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2798,31 +2782,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2831,10 +2815,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>597492</v>
+        <v>597556</v>
       </c>
       <c r="R20" t="n">
-        <v>6925938</v>
+        <v>6925836</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2866,7 +2850,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2876,7 +2860,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2903,10 +2892,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125067330</v>
+        <v>125071236</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2919,34 +2908,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>597572</v>
+        <v>597394</v>
       </c>
       <c r="R21" t="n">
-        <v>6925875</v>
+        <v>6926034</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2978,7 +2972,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2988,7 +2982,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3015,10 +3014,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125071663</v>
+        <v>125070762</v>
       </c>
       <c r="B22" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3031,16 +3030,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3051,19 +3050,19 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Svarttjärnsåsen, Mpd</t>
+          <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>597242</v>
+        <v>597398</v>
       </c>
       <c r="R22" t="n">
-        <v>6926157</v>
+        <v>6925953</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3095,7 +3094,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3105,7 +3104,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3132,10 +3136,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125067552</v>
+        <v>125071010</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3148,34 +3152,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>597549</v>
+        <v>597422</v>
       </c>
       <c r="R23" t="n">
-        <v>6925866</v>
+        <v>6925982</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3207,7 +3216,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3217,7 +3226,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3244,10 +3258,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125073564</v>
+        <v>125071368</v>
       </c>
       <c r="B24" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3260,21 +3274,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3284,10 +3298,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>597336</v>
+        <v>597351</v>
       </c>
       <c r="R24" t="n">
-        <v>6926029</v>
+        <v>6926064</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3319,7 +3333,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3329,7 +3343,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3356,10 +3370,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125067738</v>
+        <v>125067365</v>
       </c>
       <c r="B25" t="n">
-        <v>57513</v>
+        <v>96979</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3368,43 +3382,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>597512</v>
+        <v>597572</v>
       </c>
       <c r="R25" t="n">
-        <v>6925861</v>
+        <v>6925875</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3436,7 +3445,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3446,12 +3455,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:28</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3478,10 +3482,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125070603</v>
+        <v>125066963</v>
       </c>
       <c r="B26" t="n">
-        <v>96979</v>
+        <v>91012</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3490,25 +3494,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3518,10 +3522,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>597467</v>
+        <v>597575</v>
       </c>
       <c r="R26" t="n">
-        <v>6925971</v>
+        <v>6925842</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3553,7 +3557,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3563,7 +3567,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3590,10 +3594,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125066854</v>
+        <v>125067837</v>
       </c>
       <c r="B27" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3602,42 +3606,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>597598</v>
+        <v>597505</v>
       </c>
       <c r="R27" t="n">
-        <v>6925850</v>
+        <v>6925873</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 48961-2024 artfynd.xlsx
+++ b/artfynd/A 48961-2024 artfynd.xlsx
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125067978</v>
+        <v>125073564</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,39 +813,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Mpd</t>
+          <t>Svarttjärnsåsen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597505</v>
+        <v>597336</v>
       </c>
       <c r="R3" t="n">
-        <v>6925873</v>
+        <v>6926029</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,12 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:39</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125073564</v>
+        <v>125067978</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,34 +925,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svarttjärnsåsen, Mpd</t>
+          <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597336</v>
+        <v>597505</v>
       </c>
       <c r="R4" t="n">
-        <v>6926029</v>
+        <v>6925873</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +999,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125069232</v>
+        <v>125066854</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,38 +1043,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597507</v>
+        <v>597598</v>
       </c>
       <c r="R5" t="n">
-        <v>6925959</v>
+        <v>6925850</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,7 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,7 +1147,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125067330</v>
+        <v>125069232</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1183,10 +1187,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597572</v>
+        <v>597507</v>
       </c>
       <c r="R6" t="n">
-        <v>6925875</v>
+        <v>6925959</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1222,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1232,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,10 +1259,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125067046</v>
+        <v>125067330</v>
       </c>
       <c r="B7" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,33 +1271,28 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
@@ -1303,7 +1302,7 @@
         <v>597572</v>
       </c>
       <c r="R7" t="n">
-        <v>6925829</v>
+        <v>6925875</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,7 +1344,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125066854</v>
+        <v>125067046</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1384,30 +1383,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597598</v>
+        <v>597572</v>
       </c>
       <c r="R8" t="n">
-        <v>6925850</v>
+        <v>6925829</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 48961-2024 artfynd.xlsx
+++ b/artfynd/A 48961-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125073504</v>
+        <v>125071236</v>
       </c>
       <c r="B2" t="n">
         <v>57513</v>
@@ -711,19 +711,19 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Svarttjärnsåsen, Mpd</t>
+          <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597276</v>
+        <v>597394</v>
       </c>
       <c r="R2" t="n">
-        <v>6926060</v>
+        <v>6926034</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125073564</v>
+        <v>125066674</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,34 +813,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svarttjärnsåsen, Mpd</t>
+          <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597336</v>
+        <v>597627</v>
       </c>
       <c r="R3" t="n">
-        <v>6926029</v>
+        <v>6925859</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +887,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>08:39</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125067978</v>
+        <v>125067046</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,31 +931,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -954,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597505</v>
+        <v>597572</v>
       </c>
       <c r="R4" t="n">
-        <v>6925873</v>
+        <v>6925829</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,12 +1009,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:39</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125066854</v>
+        <v>125067365</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>96979</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,42 +1048,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597598</v>
+        <v>597572</v>
       </c>
       <c r="R5" t="n">
-        <v>6925850</v>
+        <v>6925875</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1121,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125069232</v>
+        <v>125071663</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,34 +1164,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Mpd</t>
+          <t>Svarttjärnsåsen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597507</v>
+        <v>597242</v>
       </c>
       <c r="R6" t="n">
-        <v>6925959</v>
+        <v>6926157</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,7 +1228,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1232,7 +1238,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,10 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125067330</v>
+        <v>125066707</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>57995</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,34 +1281,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>103018</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597572</v>
+        <v>597609</v>
       </c>
       <c r="R7" t="n">
-        <v>6925875</v>
+        <v>6925861</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1334,7 +1345,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,7 +1355,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125067046</v>
+        <v>125070603</v>
       </c>
       <c r="B8" t="n">
-        <v>56722</v>
+        <v>96979</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,39 +1398,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597572</v>
+        <v>597467</v>
       </c>
       <c r="R8" t="n">
-        <v>6925829</v>
+        <v>6925971</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1451,7 +1457,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1461,7 +1467,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125066674</v>
+        <v>125070329</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1504,39 +1510,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597627</v>
+        <v>597477</v>
       </c>
       <c r="R9" t="n">
-        <v>6925859</v>
+        <v>6925984</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1568,7 +1569,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1578,12 +1579,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:39</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1610,10 +1606,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125070603</v>
+        <v>125067837</v>
       </c>
       <c r="B10" t="n">
-        <v>96979</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1622,25 +1618,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1650,10 +1646,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597467</v>
+        <v>597505</v>
       </c>
       <c r="R10" t="n">
-        <v>6925971</v>
+        <v>6925873</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1685,7 +1681,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1695,7 +1691,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1722,7 +1718,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125068260</v>
+        <v>125067179</v>
       </c>
       <c r="B11" t="n">
         <v>57513</v>
@@ -1767,10 +1763,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597492</v>
+        <v>597556</v>
       </c>
       <c r="R11" t="n">
-        <v>6925938</v>
+        <v>6925836</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1802,7 +1798,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1812,7 +1808,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1844,10 +1840,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125067738</v>
+        <v>125071368</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1860,39 +1856,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Mpd</t>
+          <t>Svarttjärnsåsen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597512</v>
+        <v>597351</v>
       </c>
       <c r="R12" t="n">
-        <v>6925861</v>
+        <v>6926064</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1924,7 +1915,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1934,12 +1925,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1966,10 +1952,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125070329</v>
+        <v>125067552</v>
       </c>
       <c r="B13" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1982,21 +1968,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2006,10 +1992,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>597477</v>
+        <v>597549</v>
       </c>
       <c r="R13" t="n">
-        <v>6925984</v>
+        <v>6925866</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2041,7 +2027,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2051,7 +2037,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2078,10 +2064,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125071663</v>
+        <v>125067978</v>
       </c>
       <c r="B14" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2094,16 +2080,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2119,14 +2105,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Svarttjärnsåsen, Mpd</t>
+          <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>597242</v>
+        <v>597505</v>
       </c>
       <c r="R14" t="n">
-        <v>6926157</v>
+        <v>6925873</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2158,7 +2144,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2168,7 +2154,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2195,7 +2186,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125067552</v>
+        <v>125067330</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2235,10 +2226,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>597549</v>
+        <v>597572</v>
       </c>
       <c r="R15" t="n">
-        <v>6925866</v>
+        <v>6925875</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2270,7 +2261,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2280,7 +2271,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2307,10 +2298,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125068606</v>
+        <v>125069232</v>
       </c>
       <c r="B16" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2319,43 +2310,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>597492</v>
+        <v>597507</v>
       </c>
       <c r="R16" t="n">
-        <v>6925938</v>
+        <v>6925959</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2387,7 +2373,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2397,7 +2383,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2424,10 +2410,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125069803</v>
+        <v>125066854</v>
       </c>
       <c r="B17" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2436,31 +2422,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2469,10 +2454,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>597481</v>
+        <v>597598</v>
       </c>
       <c r="R17" t="n">
-        <v>6926022</v>
+        <v>6925850</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2504,7 +2489,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2514,7 +2499,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2541,10 +2526,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125066707</v>
+        <v>125069803</v>
       </c>
       <c r="B18" t="n">
-        <v>57995</v>
+        <v>56714</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2557,21 +2542,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103018</v>
+        <v>102612</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2586,10 +2571,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>597609</v>
+        <v>597481</v>
       </c>
       <c r="R18" t="n">
-        <v>6925861</v>
+        <v>6926022</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2621,7 +2606,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2631,7 +2616,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2658,10 +2643,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125069753</v>
+        <v>125068260</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2674,34 +2659,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>597481</v>
+        <v>597492</v>
       </c>
       <c r="R19" t="n">
-        <v>6926022</v>
+        <v>6925938</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2733,7 +2723,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2743,7 +2733,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2770,7 +2765,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125067179</v>
+        <v>125067738</v>
       </c>
       <c r="B20" t="n">
         <v>57513</v>
@@ -2815,10 +2810,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>597556</v>
+        <v>597512</v>
       </c>
       <c r="R20" t="n">
-        <v>6925836</v>
+        <v>6925861</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2850,7 +2845,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2860,7 +2855,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2892,7 +2887,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125071236</v>
+        <v>125071010</v>
       </c>
       <c r="B21" t="n">
         <v>57513</v>
@@ -2937,10 +2932,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>597394</v>
+        <v>597422</v>
       </c>
       <c r="R21" t="n">
-        <v>6926034</v>
+        <v>6925982</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2972,7 +2967,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2982,7 +2977,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3014,10 +3009,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125070762</v>
+        <v>125069753</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3030,39 +3025,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>597398</v>
+        <v>597481</v>
       </c>
       <c r="R22" t="n">
-        <v>6925953</v>
+        <v>6926022</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3094,7 +3084,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3104,12 +3094,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:04</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3136,7 +3121,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125071010</v>
+        <v>125073504</v>
       </c>
       <c r="B23" t="n">
         <v>57513</v>
@@ -3172,19 +3157,19 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Mpd</t>
+          <t>Svarttjärnsåsen, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>597422</v>
+        <v>597276</v>
       </c>
       <c r="R23" t="n">
-        <v>6925982</v>
+        <v>6926060</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3216,7 +3201,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3226,7 +3211,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3258,10 +3243,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125071368</v>
+        <v>125066963</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3274,34 +3259,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Svarttjärnsåsen, Mpd</t>
+          <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>597351</v>
+        <v>597575</v>
       </c>
       <c r="R24" t="n">
-        <v>6926064</v>
+        <v>6925842</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3333,7 +3318,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3343,7 +3328,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3370,10 +3355,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125067365</v>
+        <v>125068606</v>
       </c>
       <c r="B25" t="n">
-        <v>96979</v>
+        <v>56722</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3386,34 +3371,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>597572</v>
+        <v>597492</v>
       </c>
       <c r="R25" t="n">
-        <v>6925875</v>
+        <v>6925938</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3445,7 +3435,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3455,7 +3445,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3482,10 +3472,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125066963</v>
+        <v>125070762</v>
       </c>
       <c r="B26" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3498,34 +3488,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>597575</v>
+        <v>597398</v>
       </c>
       <c r="R26" t="n">
-        <v>6925842</v>
+        <v>6925953</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3557,7 +3552,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3567,7 +3562,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3594,10 +3594,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125067837</v>
+        <v>125073564</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3610,34 +3610,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Mpd</t>
+          <t>Svarttjärnsåsen, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>597505</v>
+        <v>597336</v>
       </c>
       <c r="R27" t="n">
-        <v>6925873</v>
+        <v>6926029</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 48961-2024 artfynd.xlsx
+++ b/artfynd/A 48961-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125071236</v>
+        <v>125069232</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>78947</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597394</v>
+        <v>597507</v>
       </c>
       <c r="R2" t="n">
-        <v>6926034</v>
+        <v>6925959</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125066674</v>
+        <v>125067179</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -842,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597627</v>
+        <v>597556</v>
       </c>
       <c r="R3" t="n">
-        <v>6925859</v>
+        <v>6925836</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125067046</v>
+        <v>125068606</v>
       </c>
       <c r="B4" t="n">
-        <v>56722</v>
+        <v>56836</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -964,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597572</v>
+        <v>597492</v>
       </c>
       <c r="R4" t="n">
-        <v>6925829</v>
+        <v>6925938</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125067365</v>
+        <v>125070762</v>
       </c>
       <c r="B5" t="n">
-        <v>96979</v>
+        <v>57635</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,38 +1038,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597572</v>
+        <v>597398</v>
       </c>
       <c r="R5" t="n">
-        <v>6925875</v>
+        <v>6925953</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,7 +1116,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125071663</v>
+        <v>125066963</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>91166</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,39 +1164,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Svarttjärnsåsen, Mpd</t>
+          <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597242</v>
+        <v>597575</v>
       </c>
       <c r="R6" t="n">
-        <v>6926157</v>
+        <v>6925842</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1228,7 +1223,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1238,7 +1233,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125066707</v>
+        <v>125073504</v>
       </c>
       <c r="B7" t="n">
-        <v>57995</v>
+        <v>57635</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1281,39 +1276,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103018</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Mpd</t>
+          <t>Svarttjärnsåsen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597609</v>
+        <v>597276</v>
       </c>
       <c r="R7" t="n">
-        <v>6925861</v>
+        <v>6926060</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,7 +1340,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1355,7 +1350,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125070603</v>
+        <v>125071368</v>
       </c>
       <c r="B8" t="n">
-        <v>96979</v>
+        <v>78947</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1394,38 +1394,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Mpd</t>
+          <t>Svarttjärnsåsen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597467</v>
+        <v>597351</v>
       </c>
       <c r="R8" t="n">
-        <v>6925971</v>
+        <v>6926064</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1494,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125070329</v>
+        <v>125067330</v>
       </c>
       <c r="B9" t="n">
-        <v>91012</v>
+        <v>78947</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,21 +1510,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1534,10 +1534,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597477</v>
+        <v>597572</v>
       </c>
       <c r="R9" t="n">
-        <v>6925984</v>
+        <v>6925875</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1606,10 +1606,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125067837</v>
+        <v>125071663</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>57632</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1622,34 +1622,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Mpd</t>
+          <t>Svarttjärnsåsen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597505</v>
+        <v>597242</v>
       </c>
       <c r="R10" t="n">
-        <v>6925873</v>
+        <v>6926157</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1681,7 +1686,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1691,7 +1696,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1718,10 +1723,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125067179</v>
+        <v>125067552</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>78947</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1734,39 +1739,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597556</v>
+        <v>597549</v>
       </c>
       <c r="R11" t="n">
-        <v>6925836</v>
+        <v>6925866</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1808,12 +1808,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:07</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1840,10 +1835,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125071368</v>
+        <v>125066707</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>58111</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1856,34 +1851,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>103018</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Svarttjärnsåsen, Mpd</t>
+          <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597351</v>
+        <v>597609</v>
       </c>
       <c r="R12" t="n">
-        <v>6926064</v>
+        <v>6925861</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1952,10 +1952,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125067552</v>
+        <v>125067738</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>57635</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1968,34 +1968,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>597549</v>
+        <v>597512</v>
       </c>
       <c r="R13" t="n">
-        <v>6925866</v>
+        <v>6925861</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2027,7 +2032,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2037,7 +2042,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2064,10 +2074,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125067978</v>
+        <v>125071010</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2109,10 +2119,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>597505</v>
+        <v>597422</v>
       </c>
       <c r="R14" t="n">
-        <v>6925873</v>
+        <v>6925982</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2144,7 +2154,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2154,7 +2164,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2186,10 +2196,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125067330</v>
+        <v>125067926</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>57635</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2202,34 +2212,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>597572</v>
+        <v>597505</v>
       </c>
       <c r="R15" t="n">
-        <v>6925875</v>
+        <v>6925873</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2261,7 +2276,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2271,7 +2286,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2298,10 +2318,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125069232</v>
+        <v>125071236</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>57635</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2314,34 +2334,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>597507</v>
+        <v>597394</v>
       </c>
       <c r="R16" t="n">
-        <v>6925959</v>
+        <v>6926034</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2373,7 +2398,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2383,7 +2408,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2410,10 +2440,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125066854</v>
+        <v>125067046</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>56836</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2422,30 +2452,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2454,10 +2485,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>597598</v>
+        <v>597572</v>
       </c>
       <c r="R17" t="n">
-        <v>6925850</v>
+        <v>6925829</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2489,7 +2520,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2499,7 +2530,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2526,10 +2557,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125069803</v>
+        <v>125070329</v>
       </c>
       <c r="B18" t="n">
-        <v>56714</v>
+        <v>91166</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2542,39 +2573,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>597481</v>
+        <v>597477</v>
       </c>
       <c r="R18" t="n">
-        <v>6926022</v>
+        <v>6925984</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2606,7 +2632,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2616,7 +2642,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2643,10 +2669,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125068260</v>
+        <v>125066674</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2688,10 +2714,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>597492</v>
+        <v>597627</v>
       </c>
       <c r="R19" t="n">
-        <v>6925938</v>
+        <v>6925859</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2723,7 +2749,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2733,12 +2759,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2765,10 +2791,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125067738</v>
+        <v>125067365</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>97147</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2777,43 +2803,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>597512</v>
+        <v>597572</v>
       </c>
       <c r="R20" t="n">
-        <v>6925861</v>
+        <v>6925875</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2845,7 +2866,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2855,12 +2876,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:28</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2887,10 +2903,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125071010</v>
+        <v>125073564</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>80028</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2903,39 +2919,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Mpd</t>
+          <t>Svarttjärnsåsen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>597422</v>
+        <v>597336</v>
       </c>
       <c r="R21" t="n">
-        <v>6925982</v>
+        <v>6926029</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2967,7 +2978,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2977,12 +2988,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3009,10 +3015,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125069753</v>
+        <v>125067837</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3049,10 +3055,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>597481</v>
+        <v>597505</v>
       </c>
       <c r="R22" t="n">
-        <v>6926022</v>
+        <v>6925873</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3084,7 +3090,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3094,7 +3100,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3121,10 +3127,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125073504</v>
+        <v>125069753</v>
       </c>
       <c r="B23" t="n">
-        <v>57513</v>
+        <v>78947</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3137,39 +3143,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Svarttjärnsåsen, Mpd</t>
+          <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>597276</v>
+        <v>597481</v>
       </c>
       <c r="R23" t="n">
-        <v>6926060</v>
+        <v>6926022</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3201,7 +3202,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3211,12 +3212,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3243,10 +3239,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125066963</v>
+        <v>125070603</v>
       </c>
       <c r="B24" t="n">
-        <v>91012</v>
+        <v>97147</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3255,25 +3251,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3283,10 +3279,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>597575</v>
+        <v>597467</v>
       </c>
       <c r="R24" t="n">
-        <v>6925842</v>
+        <v>6925971</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3318,7 +3314,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3328,7 +3324,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3355,10 +3351,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125068606</v>
+        <v>125069803</v>
       </c>
       <c r="B25" t="n">
-        <v>56722</v>
+        <v>56828</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3367,31 +3363,31 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3400,10 +3396,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>597492</v>
+        <v>597481</v>
       </c>
       <c r="R25" t="n">
-        <v>6925938</v>
+        <v>6926022</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3435,7 +3431,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3445,7 +3441,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3472,10 +3468,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125070762</v>
+        <v>125068260</v>
       </c>
       <c r="B26" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3508,7 +3504,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3517,10 +3513,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>597398</v>
+        <v>597492</v>
       </c>
       <c r="R26" t="n">
-        <v>6925953</v>
+        <v>6925938</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3552,7 +3548,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3562,7 +3558,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3594,10 +3590,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125073564</v>
+        <v>125066854</v>
       </c>
       <c r="B27" t="n">
-        <v>79891</v>
+        <v>98269</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3606,38 +3602,42 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Svarttjärnsåsen, Mpd</t>
+          <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>597336</v>
+        <v>597598</v>
       </c>
       <c r="R27" t="n">
-        <v>6926029</v>
+        <v>6925850</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 48961-2024 artfynd.xlsx
+++ b/artfynd/A 48961-2024 artfynd.xlsx
@@ -1382,7 +1382,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125071368</v>
+        <v>125067330</v>
       </c>
       <c r="B8" t="n">
         <v>78947</v>
@@ -1418,14 +1418,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svarttjärnsåsen, Mpd</t>
+          <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597351</v>
+        <v>597572</v>
       </c>
       <c r="R8" t="n">
-        <v>6926064</v>
+        <v>6925875</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1494,7 +1494,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125067330</v>
+        <v>125071368</v>
       </c>
       <c r="B9" t="n">
         <v>78947</v>
@@ -1530,14 +1530,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Mpd</t>
+          <t>Svarttjärnsåsen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597572</v>
+        <v>597351</v>
       </c>
       <c r="R9" t="n">
-        <v>6925875</v>
+        <v>6926064</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 48961-2024 artfynd.xlsx
+++ b/artfynd/A 48961-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125069232</v>
+        <v>125071010</v>
       </c>
       <c r="B2" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597507</v>
+        <v>597422</v>
       </c>
       <c r="R2" t="n">
-        <v>6925959</v>
+        <v>6925982</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125067179</v>
+        <v>125069232</v>
       </c>
       <c r="B3" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +813,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597556</v>
+        <v>597507</v>
       </c>
       <c r="R3" t="n">
-        <v>6925836</v>
+        <v>6925959</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:07</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125068606</v>
+        <v>125071368</v>
       </c>
       <c r="B4" t="n">
-        <v>56836</v>
+        <v>78947</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,43 +921,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Mpd</t>
+          <t>Svarttjärnsåsen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597492</v>
+        <v>597351</v>
       </c>
       <c r="R4" t="n">
-        <v>6925938</v>
+        <v>6926064</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,7 +1021,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125070762</v>
+        <v>125071236</v>
       </c>
       <c r="B5" t="n">
         <v>57635</v>
@@ -1062,7 +1057,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1071,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597398</v>
+        <v>597394</v>
       </c>
       <c r="R5" t="n">
-        <v>6925953</v>
+        <v>6926034</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1148,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125066963</v>
+        <v>125070762</v>
       </c>
       <c r="B6" t="n">
-        <v>91166</v>
+        <v>57635</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,34 +1159,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597575</v>
+        <v>597398</v>
       </c>
       <c r="R6" t="n">
-        <v>6925842</v>
+        <v>6925953</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,7 +1233,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,7 +1265,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125073504</v>
+        <v>125067179</v>
       </c>
       <c r="B7" t="n">
         <v>57635</v>
@@ -1296,19 +1301,19 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svarttjärnsåsen, Mpd</t>
+          <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597276</v>
+        <v>597556</v>
       </c>
       <c r="R7" t="n">
-        <v>6926060</v>
+        <v>6925836</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,7 +1345,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1350,7 +1355,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1382,10 +1387,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125067330</v>
+        <v>125069803</v>
       </c>
       <c r="B8" t="n">
-        <v>78947</v>
+        <v>56828</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,34 +1403,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597572</v>
+        <v>597481</v>
       </c>
       <c r="R8" t="n">
-        <v>6925875</v>
+        <v>6926022</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1457,7 +1467,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1467,7 +1477,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1494,10 +1504,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125071368</v>
+        <v>125067738</v>
       </c>
       <c r="B9" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,34 +1520,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svarttjärnsåsen, Mpd</t>
+          <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597351</v>
+        <v>597512</v>
       </c>
       <c r="R9" t="n">
-        <v>6926064</v>
+        <v>6925861</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1569,7 +1584,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1579,7 +1594,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1606,10 +1626,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125071663</v>
+        <v>125066674</v>
       </c>
       <c r="B10" t="n">
-        <v>57632</v>
+        <v>57635</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1622,16 +1642,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1647,14 +1667,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Svarttjärnsåsen, Mpd</t>
+          <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597242</v>
+        <v>597627</v>
       </c>
       <c r="R10" t="n">
-        <v>6926157</v>
+        <v>6925859</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1686,7 +1706,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1696,7 +1716,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>08:39</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1723,10 +1748,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125067552</v>
+        <v>125066707</v>
       </c>
       <c r="B11" t="n">
-        <v>78947</v>
+        <v>58111</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1739,34 +1764,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>103018</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597549</v>
+        <v>597609</v>
       </c>
       <c r="R11" t="n">
-        <v>6925866</v>
+        <v>6925861</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1798,7 +1828,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1808,7 +1838,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1835,10 +1865,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125066707</v>
+        <v>125070329</v>
       </c>
       <c r="B12" t="n">
-        <v>58111</v>
+        <v>91166</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1851,39 +1881,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103018</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597609</v>
+        <v>597477</v>
       </c>
       <c r="R12" t="n">
-        <v>6925861</v>
+        <v>6925984</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1915,7 +1940,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1925,7 +1950,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1952,7 +1977,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125067738</v>
+        <v>125068260</v>
       </c>
       <c r="B13" t="n">
         <v>57635</v>
@@ -1997,10 +2022,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>597512</v>
+        <v>597492</v>
       </c>
       <c r="R13" t="n">
-        <v>6925861</v>
+        <v>6925938</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2032,7 +2057,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2042,7 +2067,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2074,10 +2099,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125071010</v>
+        <v>125071663</v>
       </c>
       <c r="B14" t="n">
-        <v>57635</v>
+        <v>57632</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2090,16 +2115,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2115,14 +2140,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Mpd</t>
+          <t>Svarttjärnsåsen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>597422</v>
+        <v>597242</v>
       </c>
       <c r="R14" t="n">
-        <v>6925982</v>
+        <v>6926157</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2154,7 +2179,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2164,12 +2189,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2196,10 +2216,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125067926</v>
+        <v>125069753</v>
       </c>
       <c r="B15" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2212,39 +2232,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>597505</v>
+        <v>597481</v>
       </c>
       <c r="R15" t="n">
-        <v>6925873</v>
+        <v>6926022</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2276,7 +2291,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2286,12 +2301,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:37</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2318,10 +2328,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125071236</v>
+        <v>125067837</v>
       </c>
       <c r="B16" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2334,39 +2344,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>597394</v>
+        <v>597505</v>
       </c>
       <c r="R16" t="n">
-        <v>6926034</v>
+        <v>6925873</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2398,7 +2403,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2408,12 +2413,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2440,10 +2440,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125067046</v>
+        <v>125067330</v>
       </c>
       <c r="B17" t="n">
-        <v>56836</v>
+        <v>78947</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2452,33 +2452,28 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
@@ -2488,7 +2483,7 @@
         <v>597572</v>
       </c>
       <c r="R17" t="n">
-        <v>6925829</v>
+        <v>6925875</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2520,7 +2515,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2530,7 +2525,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2557,10 +2552,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125070329</v>
+        <v>125067926</v>
       </c>
       <c r="B18" t="n">
-        <v>91166</v>
+        <v>57635</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2573,34 +2568,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>597477</v>
+        <v>597505</v>
       </c>
       <c r="R18" t="n">
-        <v>6925984</v>
+        <v>6925873</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2642,7 +2642,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2669,10 +2674,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125066674</v>
+        <v>125067365</v>
       </c>
       <c r="B19" t="n">
-        <v>57635</v>
+        <v>97147</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2681,43 +2686,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>597627</v>
+        <v>597572</v>
       </c>
       <c r="R19" t="n">
-        <v>6925859</v>
+        <v>6925875</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2749,7 +2749,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2759,12 +2759,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>08:39</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2791,7 +2786,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125067365</v>
+        <v>125070603</v>
       </c>
       <c r="B20" t="n">
         <v>97147</v>
@@ -2831,10 +2826,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>597572</v>
+        <v>597467</v>
       </c>
       <c r="R20" t="n">
-        <v>6925875</v>
+        <v>6925971</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2866,7 +2861,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2876,7 +2871,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3015,7 +3010,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125067837</v>
+        <v>125067552</v>
       </c>
       <c r="B22" t="n">
         <v>78947</v>
@@ -3055,10 +3050,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>597505</v>
+        <v>597549</v>
       </c>
       <c r="R22" t="n">
-        <v>6925873</v>
+        <v>6925866</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3090,7 +3085,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3100,7 +3095,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3127,10 +3122,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125069753</v>
+        <v>125068606</v>
       </c>
       <c r="B23" t="n">
-        <v>78947</v>
+        <v>56836</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3139,38 +3134,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>597481</v>
+        <v>597492</v>
       </c>
       <c r="R23" t="n">
-        <v>6926022</v>
+        <v>6925938</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3239,10 +3239,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125070603</v>
+        <v>125073504</v>
       </c>
       <c r="B24" t="n">
-        <v>97147</v>
+        <v>57635</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3251,38 +3251,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Mpd</t>
+          <t>Svarttjärnsåsen, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>597467</v>
+        <v>597276</v>
       </c>
       <c r="R24" t="n">
-        <v>6925971</v>
+        <v>6926060</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3314,7 +3319,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3324,7 +3329,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3351,10 +3361,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125069803</v>
+        <v>125067046</v>
       </c>
       <c r="B25" t="n">
-        <v>56828</v>
+        <v>56836</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3363,31 +3373,31 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3396,10 +3406,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>597481</v>
+        <v>597572</v>
       </c>
       <c r="R25" t="n">
-        <v>6926022</v>
+        <v>6925829</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3431,7 +3441,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3441,7 +3451,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3468,10 +3478,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125068260</v>
+        <v>125066854</v>
       </c>
       <c r="B26" t="n">
-        <v>57635</v>
+        <v>98269</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3480,31 +3490,30 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3513,10 +3522,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>597492</v>
+        <v>597598</v>
       </c>
       <c r="R26" t="n">
-        <v>6925938</v>
+        <v>6925850</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3548,7 +3557,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3558,12 +3567,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:55</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3590,10 +3594,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125066854</v>
+        <v>125066963</v>
       </c>
       <c r="B27" t="n">
-        <v>98269</v>
+        <v>91166</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3602,42 +3606,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>597598</v>
+        <v>597575</v>
       </c>
       <c r="R27" t="n">
-        <v>6925850</v>
+        <v>6925842</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 48961-2024 artfynd.xlsx
+++ b/artfynd/A 48961-2024 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125071368</v>
+        <v>125071236</v>
       </c>
       <c r="B4" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,34 +925,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svarttjärnsåsen, Mpd</t>
+          <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597351</v>
+        <v>597394</v>
       </c>
       <c r="R4" t="n">
-        <v>6926064</v>
+        <v>6926034</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +999,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,7 +1031,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125071236</v>
+        <v>125070762</v>
       </c>
       <c r="B5" t="n">
         <v>57635</v>
@@ -1057,7 +1067,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1066,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597394</v>
+        <v>597398</v>
       </c>
       <c r="R5" t="n">
-        <v>6926034</v>
+        <v>6925953</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1121,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1143,7 +1153,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125070762</v>
+        <v>125067179</v>
       </c>
       <c r="B6" t="n">
         <v>57635</v>
@@ -1179,7 +1189,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1188,10 +1198,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597398</v>
+        <v>597556</v>
       </c>
       <c r="R6" t="n">
-        <v>6925953</v>
+        <v>6925836</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,7 +1243,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1265,10 +1275,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125067179</v>
+        <v>125071368</v>
       </c>
       <c r="B7" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1281,39 +1291,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Mpd</t>
+          <t>Svarttjärnsåsen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597556</v>
+        <v>597351</v>
       </c>
       <c r="R7" t="n">
-        <v>6925836</v>
+        <v>6926064</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,7 +1350,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1355,12 +1360,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:07</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1626,10 +1626,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125066674</v>
+        <v>125066707</v>
       </c>
       <c r="B10" t="n">
-        <v>57635</v>
+        <v>58111</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1642,27 +1642,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>103018</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1671,10 +1671,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597627</v>
+        <v>597609</v>
       </c>
       <c r="R10" t="n">
-        <v>6925859</v>
+        <v>6925861</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1716,12 +1716,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:39</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1748,10 +1743,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125066707</v>
+        <v>125066674</v>
       </c>
       <c r="B11" t="n">
-        <v>58111</v>
+        <v>57635</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1764,27 +1759,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103018</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1793,10 +1788,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597609</v>
+        <v>597627</v>
       </c>
       <c r="R11" t="n">
-        <v>6925861</v>
+        <v>6925859</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1828,7 +1823,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1838,7 +1833,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:39</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2099,10 +2099,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125071663</v>
+        <v>125069753</v>
       </c>
       <c r="B14" t="n">
-        <v>57632</v>
+        <v>78947</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2115,39 +2115,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Svarttjärnsåsen, Mpd</t>
+          <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>597242</v>
+        <v>597481</v>
       </c>
       <c r="R14" t="n">
-        <v>6926157</v>
+        <v>6926022</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2179,7 +2174,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2189,7 +2184,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2216,7 +2211,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125069753</v>
+        <v>125067837</v>
       </c>
       <c r="B15" t="n">
         <v>78947</v>
@@ -2256,10 +2251,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>597481</v>
+        <v>597505</v>
       </c>
       <c r="R15" t="n">
-        <v>6926022</v>
+        <v>6925873</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2291,7 +2286,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2301,7 +2296,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2328,7 +2323,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125067837</v>
+        <v>125067330</v>
       </c>
       <c r="B16" t="n">
         <v>78947</v>
@@ -2368,10 +2363,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>597505</v>
+        <v>597572</v>
       </c>
       <c r="R16" t="n">
-        <v>6925873</v>
+        <v>6925875</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2403,7 +2398,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2413,7 +2408,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2440,10 +2435,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125067330</v>
+        <v>125071663</v>
       </c>
       <c r="B17" t="n">
-        <v>78947</v>
+        <v>57632</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2456,34 +2451,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Mpd</t>
+          <t>Svarttjärnsåsen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>597572</v>
+        <v>597242</v>
       </c>
       <c r="R17" t="n">
-        <v>6925875</v>
+        <v>6926157</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2515,7 +2515,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 48961-2024 artfynd.xlsx
+++ b/artfynd/A 48961-2024 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125071236</v>
+        <v>125071368</v>
       </c>
       <c r="B4" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,39 +925,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Mpd</t>
+          <t>Svarttjärnsåsen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597394</v>
+        <v>597351</v>
       </c>
       <c r="R4" t="n">
-        <v>6926034</v>
+        <v>6926064</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,12 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,7 +1021,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125070762</v>
+        <v>125071236</v>
       </c>
       <c r="B5" t="n">
         <v>57635</v>
@@ -1067,7 +1057,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1076,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597398</v>
+        <v>597394</v>
       </c>
       <c r="R5" t="n">
-        <v>6925953</v>
+        <v>6926034</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1153,7 +1143,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125067179</v>
+        <v>125070762</v>
       </c>
       <c r="B6" t="n">
         <v>57635</v>
@@ -1189,7 +1179,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1198,10 +1188,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597556</v>
+        <v>597398</v>
       </c>
       <c r="R6" t="n">
-        <v>6925836</v>
+        <v>6925953</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1223,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,7 +1233,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1275,10 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125071368</v>
+        <v>125067179</v>
       </c>
       <c r="B7" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1291,34 +1281,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svarttjärnsåsen, Mpd</t>
+          <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597351</v>
+        <v>597556</v>
       </c>
       <c r="R7" t="n">
-        <v>6926064</v>
+        <v>6925836</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1350,7 +1345,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1360,7 +1355,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1626,10 +1626,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125066707</v>
+        <v>125066674</v>
       </c>
       <c r="B10" t="n">
-        <v>58111</v>
+        <v>57635</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1642,27 +1642,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103018</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1671,10 +1671,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597609</v>
+        <v>597627</v>
       </c>
       <c r="R10" t="n">
-        <v>6925861</v>
+        <v>6925859</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1716,7 +1716,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:39</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1743,10 +1748,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125066674</v>
+        <v>125066707</v>
       </c>
       <c r="B11" t="n">
-        <v>57635</v>
+        <v>58111</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1759,27 +1764,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>103018</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1788,10 +1793,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597627</v>
+        <v>597609</v>
       </c>
       <c r="R11" t="n">
-        <v>6925859</v>
+        <v>6925861</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1823,7 +1828,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1833,12 +1838,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:39</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 48961-2024 artfynd.xlsx
+++ b/artfynd/A 48961-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125071010</v>
+        <v>125067330</v>
       </c>
       <c r="B2" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597422</v>
+        <v>597572</v>
       </c>
       <c r="R2" t="n">
-        <v>6925982</v>
+        <v>6925875</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125069232</v>
+        <v>125073564</v>
       </c>
       <c r="B3" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Mpd</t>
+          <t>Svarttjärnsåsen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597507</v>
+        <v>597336</v>
       </c>
       <c r="R3" t="n">
-        <v>6925959</v>
+        <v>6926029</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125071368</v>
+        <v>125073504</v>
       </c>
       <c r="B4" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,34 +900,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Svarttjärnsåsen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597351</v>
+        <v>597276</v>
       </c>
       <c r="R4" t="n">
-        <v>6926064</v>
+        <v>6926060</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +974,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,15 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125071236</v>
+        <v>125069232</v>
       </c>
       <c r="B5" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1037,39 +1017,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597394</v>
+        <v>597507</v>
       </c>
       <c r="R5" t="n">
-        <v>6926034</v>
+        <v>6925959</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,12 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,15 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125070762</v>
+        <v>125070329</v>
       </c>
       <c r="B6" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1159,39 +1124,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597398</v>
+        <v>597477</v>
       </c>
       <c r="R6" t="n">
-        <v>6925953</v>
+        <v>6925984</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,12 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:04</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,15 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125067179</v>
+        <v>125067926</v>
       </c>
       <c r="B7" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,7 +1251,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1310,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597556</v>
+        <v>597505</v>
       </c>
       <c r="R7" t="n">
-        <v>6925836</v>
+        <v>6925873</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,7 +1295,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1355,7 +1305,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1390,12 +1340,7 @@
         <v>125069803</v>
       </c>
       <c r="B8" t="n">
-        <v>56828</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56834</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1504,43 +1449,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125067738</v>
+        <v>125068606</v>
       </c>
       <c r="B9" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56843</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1549,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597512</v>
+        <v>597492</v>
       </c>
       <c r="R9" t="n">
-        <v>6925861</v>
+        <v>6925938</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1584,7 +1524,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1594,12 +1534,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:28</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1626,43 +1561,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125066674</v>
+        <v>125066854</v>
       </c>
       <c r="B10" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1671,10 +1600,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597627</v>
+        <v>597598</v>
       </c>
       <c r="R10" t="n">
-        <v>6925859</v>
+        <v>6925850</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1706,7 +1635,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1716,12 +1645,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:39</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1748,43 +1672,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125066707</v>
+        <v>125067046</v>
       </c>
       <c r="B11" t="n">
-        <v>58111</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56843</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103018</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1793,10 +1712,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597609</v>
+        <v>597572</v>
       </c>
       <c r="R11" t="n">
-        <v>6925861</v>
+        <v>6925829</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1828,7 +1747,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1838,7 +1757,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1865,15 +1784,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125070329</v>
+        <v>125071368</v>
       </c>
       <c r="B12" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1881,34 +1795,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Mpd</t>
+          <t>Svarttjärnsåsen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597477</v>
+        <v>597351</v>
       </c>
       <c r="R12" t="n">
-        <v>6925984</v>
+        <v>6926064</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1940,7 +1854,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1950,7 +1864,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1977,15 +1891,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125068260</v>
+        <v>125066963</v>
       </c>
       <c r="B13" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1993,39 +1902,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>597492</v>
+        <v>597575</v>
       </c>
       <c r="R13" t="n">
-        <v>6925938</v>
+        <v>6925842</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2057,7 +1961,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2067,12 +1971,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:55</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2099,15 +1998,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125069753</v>
+        <v>125066707</v>
       </c>
       <c r="B14" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58129</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2115,34 +2009,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>103018</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>597481</v>
+        <v>597609</v>
       </c>
       <c r="R14" t="n">
-        <v>6926022</v>
+        <v>6925861</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2174,7 +2073,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2184,7 +2083,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2211,15 +2110,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125067837</v>
+        <v>125071010</v>
       </c>
       <c r="B15" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2227,34 +2121,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>597505</v>
+        <v>597422</v>
       </c>
       <c r="R15" t="n">
-        <v>6925873</v>
+        <v>6925982</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2286,7 +2185,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2296,7 +2195,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2323,15 +2227,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125067330</v>
+        <v>125066674</v>
       </c>
       <c r="B16" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2339,34 +2238,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>597572</v>
+        <v>597627</v>
       </c>
       <c r="R16" t="n">
-        <v>6925875</v>
+        <v>6925859</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2398,7 +2302,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2408,7 +2312,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>08:39</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2435,15 +2344,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125071663</v>
+        <v>125067179</v>
       </c>
       <c r="B17" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2451,16 +2355,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2476,14 +2380,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Svarttjärnsåsen, Mpd</t>
+          <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>597242</v>
+        <v>597556</v>
       </c>
       <c r="R17" t="n">
-        <v>6926157</v>
+        <v>6925836</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2515,7 +2419,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2525,7 +2429,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2552,15 +2461,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125067926</v>
+        <v>125067738</v>
       </c>
       <c r="B18" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2588,7 +2492,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2597,10 +2501,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>597505</v>
+        <v>597512</v>
       </c>
       <c r="R18" t="n">
-        <v>6925873</v>
+        <v>6925861</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2632,7 +2536,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2642,7 +2546,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2674,50 +2578,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125067365</v>
+        <v>125068260</v>
       </c>
       <c r="B19" t="n">
-        <v>97147</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>597572</v>
+        <v>597492</v>
       </c>
       <c r="R19" t="n">
-        <v>6925875</v>
+        <v>6925938</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2749,7 +2653,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2759,7 +2663,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2786,37 +2695,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125070603</v>
+        <v>125069753</v>
       </c>
       <c r="B20" t="n">
-        <v>97147</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2826,10 +2730,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>597467</v>
+        <v>597481</v>
       </c>
       <c r="R20" t="n">
-        <v>6925971</v>
+        <v>6926022</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2861,7 +2765,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2871,7 +2775,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2898,15 +2802,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125073564</v>
+        <v>125071236</v>
       </c>
       <c r="B21" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2914,34 +2813,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Svarttjärnsåsen, Mpd</t>
+          <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>597336</v>
+        <v>597394</v>
       </c>
       <c r="R21" t="n">
-        <v>6926029</v>
+        <v>6926034</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2973,7 +2877,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2983,7 +2887,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3010,15 +2919,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125067552</v>
+        <v>125070762</v>
       </c>
       <c r="B22" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3026,34 +2930,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>597549</v>
+        <v>597398</v>
       </c>
       <c r="R22" t="n">
-        <v>6925866</v>
+        <v>6925953</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3085,7 +2994,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3095,7 +3004,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3122,55 +3036,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125068606</v>
+        <v>125071663</v>
       </c>
       <c r="B23" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Mpd</t>
+          <t>Svarttjärnsåsen, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>597492</v>
+        <v>597242</v>
       </c>
       <c r="R23" t="n">
-        <v>6925938</v>
+        <v>6926157</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3202,7 +3111,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3212,7 +3121,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3239,55 +3148,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125073504</v>
+        <v>125070603</v>
       </c>
       <c r="B24" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97202</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Svarttjärnsåsen, Mpd</t>
+          <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>597276</v>
+        <v>597467</v>
       </c>
       <c r="R24" t="n">
-        <v>6926060</v>
+        <v>6925971</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3319,7 +3218,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3329,12 +3228,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3361,15 +3255,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125067046</v>
+        <v>125067365</v>
       </c>
       <c r="B25" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97202</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3377,29 +3266,24 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
@@ -3409,7 +3293,7 @@
         <v>597572</v>
       </c>
       <c r="R25" t="n">
-        <v>6925829</v>
+        <v>6925875</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3441,7 +3325,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3451,7 +3335,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3478,54 +3362,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125066854</v>
+        <v>125067552</v>
       </c>
       <c r="B26" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>597598</v>
+        <v>597549</v>
       </c>
       <c r="R26" t="n">
-        <v>6925850</v>
+        <v>6925866</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3557,7 +3432,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3567,7 +3442,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3594,15 +3469,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125066963</v>
+        <v>125067837</v>
       </c>
       <c r="B27" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3610,21 +3480,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3634,10 +3504,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>597575</v>
+        <v>597505</v>
       </c>
       <c r="R27" t="n">
-        <v>6925842</v>
+        <v>6925873</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3669,7 +3539,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3679,7 +3549,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 48961-2024 artfynd.xlsx
+++ b/artfynd/A 48961-2024 artfynd.xlsx
@@ -3039,7 +3039,7 @@
         <v>125071663</v>
       </c>
       <c r="B23" t="n">
-        <v>57648</v>
+        <v>57658</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 48961-2024 artfynd.xlsx
+++ b/artfynd/A 48961-2024 artfynd.xlsx
@@ -3039,7 +3039,7 @@
         <v>125071663</v>
       </c>
       <c r="B23" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 48961-2024 artfynd.xlsx
+++ b/artfynd/A 48961-2024 artfynd.xlsx
@@ -3039,7 +3039,7 @@
         <v>125071663</v>
       </c>
       <c r="B23" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 48961-2024 artfynd.xlsx
+++ b/artfynd/A 48961-2024 artfynd.xlsx
@@ -3039,7 +3039,7 @@
         <v>125071663</v>
       </c>
       <c r="B23" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 48961-2024 artfynd.xlsx
+++ b/artfynd/A 48961-2024 artfynd.xlsx
@@ -3039,7 +3039,7 @@
         <v>125071663</v>
       </c>
       <c r="B23" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 48961-2024 artfynd.xlsx
+++ b/artfynd/A 48961-2024 artfynd.xlsx
@@ -3039,7 +3039,7 @@
         <v>125071663</v>
       </c>
       <c r="B23" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 48961-2024 artfynd.xlsx
+++ b/artfynd/A 48961-2024 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>125073504</v>
       </c>
       <c r="B4" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>125067926</v>
       </c>
       <c r="B7" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>125071010</v>
       </c>
       <c r="B15" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>125066674</v>
       </c>
       <c r="B16" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>125067179</v>
       </c>
       <c r="B17" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>125067738</v>
       </c>
       <c r="B18" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         <v>125068260</v>
       </c>
       <c r="B19" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>125071236</v>
       </c>
       <c r="B21" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>125070762</v>
       </c>
       <c r="B22" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 48961-2024 artfynd.xlsx
+++ b/artfynd/A 48961-2024 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>125073504</v>
       </c>
       <c r="B4" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>125067926</v>
       </c>
       <c r="B7" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>125071010</v>
       </c>
       <c r="B15" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>125066674</v>
       </c>
       <c r="B16" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>125067179</v>
       </c>
       <c r="B17" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>125067738</v>
       </c>
       <c r="B18" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         <v>125068260</v>
       </c>
       <c r="B19" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>125071236</v>
       </c>
       <c r="B21" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>125070762</v>
       </c>
       <c r="B22" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 48961-2024 artfynd.xlsx
+++ b/artfynd/A 48961-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125067330</v>
+        <v>125066963</v>
       </c>
       <c r="B2" t="n">
-        <v>78967</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597572</v>
+        <v>597575</v>
       </c>
       <c r="R2" t="n">
-        <v>6925875</v>
+        <v>6925842</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125073564</v>
+        <v>125070329</v>
       </c>
       <c r="B3" t="n">
-        <v>80070</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svarttjärnsåsen, Mpd</t>
+          <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597336</v>
+        <v>597477</v>
       </c>
       <c r="R3" t="n">
-        <v>6926029</v>
+        <v>6925984</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,50 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125073504</v>
+        <v>125066583</v>
       </c>
       <c r="B4" t="n">
-        <v>57741</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svarttjärnsåsen, Mpd</t>
+          <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597276</v>
+        <v>597638</v>
       </c>
       <c r="R4" t="n">
-        <v>6926060</v>
+        <v>6925877</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,12 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,14 +996,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125069232</v>
+        <v>125067330</v>
       </c>
       <c r="B5" t="n">
-        <v>78967</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1041,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597507</v>
+        <v>597572</v>
       </c>
       <c r="R5" t="n">
-        <v>6925959</v>
+        <v>6925875</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,32 +1103,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125070329</v>
+        <v>125067552</v>
       </c>
       <c r="B6" t="n">
-        <v>91220</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1148,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597477</v>
+        <v>597549</v>
       </c>
       <c r="R6" t="n">
-        <v>6925984</v>
+        <v>6925866</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,40 +1210,35 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125067926</v>
+        <v>125067837</v>
       </c>
       <c r="B7" t="n">
-        <v>57741</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
@@ -1295,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1305,12 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:37</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,50 +1317,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125069803</v>
+        <v>125069232</v>
       </c>
       <c r="B8" t="n">
-        <v>56834</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597481</v>
+        <v>597507</v>
       </c>
       <c r="R8" t="n">
-        <v>6926022</v>
+        <v>6925959</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1412,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1422,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1449,50 +1424,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125068606</v>
+        <v>125069753</v>
       </c>
       <c r="B9" t="n">
-        <v>56843</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597492</v>
+        <v>597481</v>
       </c>
       <c r="R9" t="n">
-        <v>6925938</v>
+        <v>6926022</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1534,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1561,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125066854</v>
+        <v>125071175</v>
       </c>
       <c r="B10" t="n">
-        <v>98324</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,38 +1542,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597598</v>
+        <v>597414</v>
       </c>
       <c r="R10" t="n">
-        <v>6925850</v>
+        <v>6926038</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1635,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1645,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1672,50 +1638,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125067046</v>
+        <v>125071368</v>
       </c>
       <c r="B11" t="n">
-        <v>56843</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Mpd</t>
+          <t>Svarttjärnsåsen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597572</v>
+        <v>597351</v>
       </c>
       <c r="R11" t="n">
-        <v>6925829</v>
+        <v>6926064</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1747,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1757,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1784,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125071368</v>
+        <v>125073564</v>
       </c>
       <c r="B12" t="n">
-        <v>78967</v>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1795,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1819,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597351</v>
+        <v>597336</v>
       </c>
       <c r="R12" t="n">
-        <v>6926064</v>
+        <v>6926029</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1854,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1864,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1891,45 +1852,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125066963</v>
+        <v>125071663</v>
       </c>
       <c r="B13" t="n">
-        <v>91220</v>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Mpd</t>
+          <t>Svarttjärnsåsen, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>597575</v>
+        <v>597242</v>
       </c>
       <c r="R13" t="n">
-        <v>6925842</v>
+        <v>6926157</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1961,7 +1927,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1971,7 +1937,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1998,10 +1964,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125066707</v>
+        <v>125066674</v>
       </c>
       <c r="B14" t="n">
-        <v>58129</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,27 +1975,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103018</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2038,10 +2004,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>597609</v>
+        <v>597627</v>
       </c>
       <c r="R14" t="n">
-        <v>6925861</v>
+        <v>6925859</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2073,7 +2039,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2083,7 +2049,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:39</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2110,10 +2081,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125071010</v>
+        <v>125067179</v>
       </c>
       <c r="B15" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2150,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>597422</v>
+        <v>597556</v>
       </c>
       <c r="R15" t="n">
-        <v>6925982</v>
+        <v>6925836</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2185,7 +2156,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2195,7 +2166,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2227,10 +2198,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125066674</v>
+        <v>125067738</v>
       </c>
       <c r="B16" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2267,10 +2238,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>597627</v>
+        <v>597512</v>
       </c>
       <c r="R16" t="n">
-        <v>6925859</v>
+        <v>6925861</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2302,7 +2273,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2312,12 +2283,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2344,10 +2315,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125067179</v>
+        <v>125067926</v>
       </c>
       <c r="B17" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2375,7 +2346,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2384,10 +2355,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>597556</v>
+        <v>597505</v>
       </c>
       <c r="R17" t="n">
-        <v>6925836</v>
+        <v>6925873</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2419,7 +2390,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2429,7 +2400,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2461,10 +2432,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125067738</v>
+        <v>125068260</v>
       </c>
       <c r="B18" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2501,10 +2472,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>597512</v>
+        <v>597492</v>
       </c>
       <c r="R18" t="n">
-        <v>6925861</v>
+        <v>6925938</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2536,7 +2507,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2546,7 +2517,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2578,10 +2549,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125068260</v>
+        <v>125070762</v>
       </c>
       <c r="B19" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,7 +2580,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2618,10 +2589,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>597492</v>
+        <v>597398</v>
       </c>
       <c r="R19" t="n">
-        <v>6925938</v>
+        <v>6925953</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2653,7 +2624,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2663,7 +2634,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2695,10 +2666,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125069753</v>
+        <v>125071010</v>
       </c>
       <c r="B20" t="n">
-        <v>78967</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2706,34 +2677,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>597481</v>
+        <v>597422</v>
       </c>
       <c r="R20" t="n">
-        <v>6926022</v>
+        <v>6925982</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2765,7 +2741,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2775,7 +2751,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2805,7 +2786,7 @@
         <v>125071236</v>
       </c>
       <c r="B21" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2919,10 +2900,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125070762</v>
+        <v>125073504</v>
       </c>
       <c r="B22" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2955,14 +2936,14 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Mpd</t>
+          <t>Svarttjärnsåsen, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>597398</v>
+        <v>597276</v>
       </c>
       <c r="R22" t="n">
-        <v>6925953</v>
+        <v>6926060</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2994,7 +2975,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3004,7 +2985,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3036,50 +3017,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125071663</v>
+        <v>125067046</v>
       </c>
       <c r="B23" t="n">
-        <v>57681</v>
+        <v>57141</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Svarttjärnsåsen, Mpd</t>
+          <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>597242</v>
+        <v>597572</v>
       </c>
       <c r="R23" t="n">
-        <v>6926157</v>
+        <v>6925829</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3111,7 +3092,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3121,7 +3102,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3148,10 +3129,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125070603</v>
+        <v>125068606</v>
       </c>
       <c r="B24" t="n">
-        <v>97202</v>
+        <v>57141</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3159,34 +3140,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>597467</v>
+        <v>597492</v>
       </c>
       <c r="R24" t="n">
-        <v>6925971</v>
+        <v>6925938</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3218,7 +3204,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3228,7 +3214,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3255,10 +3241,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125067365</v>
+        <v>125069803</v>
       </c>
       <c r="B25" t="n">
-        <v>97202</v>
+        <v>57132</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3266,34 +3252,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>102612</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>597572</v>
+        <v>597481</v>
       </c>
       <c r="R25" t="n">
-        <v>6925875</v>
+        <v>6926022</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3325,7 +3316,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3335,7 +3326,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3362,45 +3353,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125067552</v>
+        <v>125066707</v>
       </c>
       <c r="B26" t="n">
-        <v>78967</v>
+        <v>58439</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>103018</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>597549</v>
+        <v>597609</v>
       </c>
       <c r="R26" t="n">
-        <v>6925866</v>
+        <v>6925861</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3432,7 +3428,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3442,7 +3438,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3469,10 +3465,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125067837</v>
+        <v>125071777</v>
       </c>
       <c r="B27" t="n">
-        <v>78967</v>
+        <v>58114</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3480,34 +3476,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Mpd</t>
+          <t>Svarttjärnsåsen, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>597505</v>
+        <v>597222</v>
       </c>
       <c r="R27" t="n">
-        <v>6925873</v>
+        <v>6926113</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3539,7 +3543,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3549,7 +3553,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3573,6 +3577,331 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>125066854</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>597598</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6925850</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>125067365</v>
+      </c>
+      <c r="B29" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>597572</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6925875</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>125070603</v>
+      </c>
+      <c r="B30" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>597467</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6925971</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48961-2024 artfynd.xlsx
+++ b/artfynd/A 48961-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125066963</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070329</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125066583</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125067330</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125067552</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125067837</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125069232</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125069753</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125071175</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125071368</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125073564</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1961,6 +2021,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125071663</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2078,6 +2143,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125066674</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2195,6 +2265,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125067179</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2312,6 +2387,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125067738</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2429,6 +2509,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125067926</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2546,6 +2631,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125068260</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2663,6 +2753,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070762</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2780,6 +2875,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125071010</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2897,6 +2997,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125071236</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3014,6 +3119,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125073504</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3126,6 +3236,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125067046</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3238,6 +3353,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125068606</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3350,6 +3470,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125069803</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3462,6 +3587,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125066707</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3577,6 +3707,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125071777</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3688,6 +3823,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125066854</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3795,6 +3935,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125067365</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3902,8 +4047,44 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070603</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>